--- a/data/trans_orig/IP2902-Provincia-trans_orig.xlsx
+++ b/data/trans_orig/IP2902-Provincia-trans_orig.xlsx
@@ -732,12 +732,12 @@
       </c>
       <c r="E4" s="2" t="inlineStr">
         <is>
-          <t>4332</t>
+          <t>4392</t>
         </is>
       </c>
       <c r="F4" s="2" t="inlineStr">
         <is>
-          <t>11884</t>
+          <t>12086</t>
         </is>
       </c>
       <c r="G4" s="2" t="inlineStr">
@@ -747,12 +747,12 @@
       </c>
       <c r="H4" s="2" t="inlineStr">
         <is>
-          <t>8,88%</t>
+          <t>9,0%</t>
         </is>
       </c>
       <c r="I4" s="2" t="inlineStr">
         <is>
-          <t>24,36%</t>
+          <t>24,78%</t>
         </is>
       </c>
       <c r="J4" s="2" t="inlineStr">
@@ -767,12 +767,12 @@
       </c>
       <c r="L4" s="2" t="inlineStr">
         <is>
-          <t>5254</t>
+          <t>5089</t>
         </is>
       </c>
       <c r="M4" s="2" t="inlineStr">
         <is>
-          <t>14774</t>
+          <t>14869</t>
         </is>
       </c>
       <c r="N4" s="2" t="inlineStr">
@@ -782,12 +782,12 @@
       </c>
       <c r="O4" s="2" t="inlineStr">
         <is>
-          <t>9,28%</t>
+          <t>8,99%</t>
         </is>
       </c>
       <c r="P4" s="2" t="inlineStr">
         <is>
-          <t>26,09%</t>
+          <t>26,26%</t>
         </is>
       </c>
       <c r="Q4" s="2" t="inlineStr">
@@ -802,12 +802,12 @@
       </c>
       <c r="S4" s="2" t="inlineStr">
         <is>
-          <t>11721</t>
+          <t>11126</t>
         </is>
       </c>
       <c r="T4" s="2" t="inlineStr">
         <is>
-          <t>23575</t>
+          <t>23624</t>
         </is>
       </c>
       <c r="U4" s="2" t="inlineStr">
@@ -817,12 +817,12 @@
       </c>
       <c r="V4" s="2" t="inlineStr">
         <is>
-          <t>11,12%</t>
+          <t>10,56%</t>
         </is>
       </c>
       <c r="W4" s="2" t="inlineStr">
         <is>
-          <t>22,37%</t>
+          <t>22,41%</t>
         </is>
       </c>
     </row>
@@ -845,12 +845,12 @@
       </c>
       <c r="E5" s="2" t="inlineStr">
         <is>
-          <t>5394</t>
+          <t>5489</t>
         </is>
       </c>
       <c r="F5" s="2" t="inlineStr">
         <is>
-          <t>13870</t>
+          <t>13807</t>
         </is>
       </c>
       <c r="G5" s="2" t="inlineStr">
@@ -860,12 +860,12 @@
       </c>
       <c r="H5" s="2" t="inlineStr">
         <is>
-          <t>11,06%</t>
+          <t>11,25%</t>
         </is>
       </c>
       <c r="I5" s="2" t="inlineStr">
         <is>
-          <t>28,43%</t>
+          <t>28,3%</t>
         </is>
       </c>
       <c r="J5" s="2" t="inlineStr">
@@ -880,12 +880,12 @@
       </c>
       <c r="L5" s="2" t="inlineStr">
         <is>
-          <t>7699</t>
+          <t>7849</t>
         </is>
       </c>
       <c r="M5" s="2" t="inlineStr">
         <is>
-          <t>18447</t>
+          <t>18570</t>
         </is>
       </c>
       <c r="N5" s="2" t="inlineStr">
@@ -895,12 +895,12 @@
       </c>
       <c r="O5" s="2" t="inlineStr">
         <is>
-          <t>13,6%</t>
+          <t>13,86%</t>
         </is>
       </c>
       <c r="P5" s="2" t="inlineStr">
         <is>
-          <t>32,58%</t>
+          <t>32,8%</t>
         </is>
       </c>
       <c r="Q5" s="2" t="inlineStr">
@@ -915,12 +915,12 @@
       </c>
       <c r="S5" s="2" t="inlineStr">
         <is>
-          <t>15549</t>
+          <t>15523</t>
         </is>
       </c>
       <c r="T5" s="2" t="inlineStr">
         <is>
-          <t>28747</t>
+          <t>28498</t>
         </is>
       </c>
       <c r="U5" s="2" t="inlineStr">
@@ -930,12 +930,12 @@
       </c>
       <c r="V5" s="2" t="inlineStr">
         <is>
-          <t>14,75%</t>
+          <t>14,73%</t>
         </is>
       </c>
       <c r="W5" s="2" t="inlineStr">
         <is>
-          <t>27,27%</t>
+          <t>27,04%</t>
         </is>
       </c>
     </row>
@@ -958,12 +958,12 @@
       </c>
       <c r="E6" s="2" t="inlineStr">
         <is>
-          <t>26757</t>
+          <t>26621</t>
         </is>
       </c>
       <c r="F6" s="2" t="inlineStr">
         <is>
-          <t>36704</t>
+          <t>37073</t>
         </is>
       </c>
       <c r="G6" s="2" t="inlineStr">
@@ -973,12 +973,12 @@
       </c>
       <c r="H6" s="2" t="inlineStr">
         <is>
-          <t>54,85%</t>
+          <t>54,57%</t>
         </is>
       </c>
       <c r="I6" s="2" t="inlineStr">
         <is>
-          <t>75,24%</t>
+          <t>75,99%</t>
         </is>
       </c>
       <c r="J6" s="2" t="inlineStr">
@@ -993,12 +993,12 @@
       </c>
       <c r="L6" s="2" t="inlineStr">
         <is>
-          <t>28471</t>
+          <t>28821</t>
         </is>
       </c>
       <c r="M6" s="2" t="inlineStr">
         <is>
-          <t>40715</t>
+          <t>40757</t>
         </is>
       </c>
       <c r="N6" s="2" t="inlineStr">
@@ -1008,12 +1008,12 @@
       </c>
       <c r="O6" s="2" t="inlineStr">
         <is>
-          <t>50,29%</t>
+          <t>50,91%</t>
         </is>
       </c>
       <c r="P6" s="2" t="inlineStr">
         <is>
-          <t>71,91%</t>
+          <t>71,99%</t>
         </is>
       </c>
       <c r="Q6" s="2" t="inlineStr">
@@ -1028,12 +1028,12 @@
       </c>
       <c r="S6" s="2" t="inlineStr">
         <is>
-          <t>58957</t>
+          <t>59109</t>
         </is>
       </c>
       <c r="T6" s="2" t="inlineStr">
         <is>
-          <t>74654</t>
+          <t>74691</t>
         </is>
       </c>
       <c r="U6" s="2" t="inlineStr">
@@ -1043,12 +1043,12 @@
       </c>
       <c r="V6" s="2" t="inlineStr">
         <is>
-          <t>55,94%</t>
+          <t>56,08%</t>
         </is>
       </c>
       <c r="W6" s="2" t="inlineStr">
         <is>
-          <t>70,83%</t>
+          <t>70,86%</t>
         </is>
       </c>
     </row>
@@ -1188,12 +1188,12 @@
       </c>
       <c r="E8" s="2" t="inlineStr">
         <is>
-          <t>27124</t>
+          <t>27435</t>
         </is>
       </c>
       <c r="F8" s="2" t="inlineStr">
         <is>
-          <t>42823</t>
+          <t>42594</t>
         </is>
       </c>
       <c r="G8" s="2" t="inlineStr">
@@ -1203,12 +1203,12 @@
       </c>
       <c r="H8" s="2" t="inlineStr">
         <is>
-          <t>26,71%</t>
+          <t>27,01%</t>
         </is>
       </c>
       <c r="I8" s="2" t="inlineStr">
         <is>
-          <t>42,16%</t>
+          <t>41,94%</t>
         </is>
       </c>
       <c r="J8" s="2" t="inlineStr">
@@ -1223,12 +1223,12 @@
       </c>
       <c r="L8" s="2" t="inlineStr">
         <is>
-          <t>26099</t>
+          <t>26076</t>
         </is>
       </c>
       <c r="M8" s="2" t="inlineStr">
         <is>
-          <t>42419</t>
+          <t>41151</t>
         </is>
       </c>
       <c r="N8" s="2" t="inlineStr">
@@ -1238,12 +1238,12 @@
       </c>
       <c r="O8" s="2" t="inlineStr">
         <is>
-          <t>24,29%</t>
+          <t>24,26%</t>
         </is>
       </c>
       <c r="P8" s="2" t="inlineStr">
         <is>
-          <t>39,47%</t>
+          <t>38,29%</t>
         </is>
       </c>
       <c r="Q8" s="2" t="inlineStr">
@@ -1258,12 +1258,12 @@
       </c>
       <c r="S8" s="2" t="inlineStr">
         <is>
-          <t>57781</t>
+          <t>58448</t>
         </is>
       </c>
       <c r="T8" s="2" t="inlineStr">
         <is>
-          <t>79304</t>
+          <t>78792</t>
         </is>
       </c>
       <c r="U8" s="2" t="inlineStr">
@@ -1273,12 +1273,12 @@
       </c>
       <c r="V8" s="2" t="inlineStr">
         <is>
-          <t>27,64%</t>
+          <t>27,96%</t>
         </is>
       </c>
       <c r="W8" s="2" t="inlineStr">
         <is>
-          <t>37,94%</t>
+          <t>37,69%</t>
         </is>
       </c>
     </row>
@@ -1301,12 +1301,12 @@
       </c>
       <c r="E9" s="2" t="inlineStr">
         <is>
-          <t>8266</t>
+          <t>7997</t>
         </is>
       </c>
       <c r="F9" s="2" t="inlineStr">
         <is>
-          <t>18841</t>
+          <t>19122</t>
         </is>
       </c>
       <c r="G9" s="2" t="inlineStr">
@@ -1316,12 +1316,12 @@
       </c>
       <c r="H9" s="2" t="inlineStr">
         <is>
-          <t>8,14%</t>
+          <t>7,87%</t>
         </is>
       </c>
       <c r="I9" s="2" t="inlineStr">
         <is>
-          <t>18,55%</t>
+          <t>18,83%</t>
         </is>
       </c>
       <c r="J9" s="2" t="inlineStr">
@@ -1336,12 +1336,12 @@
       </c>
       <c r="L9" s="2" t="inlineStr">
         <is>
-          <t>7133</t>
+          <t>7290</t>
         </is>
       </c>
       <c r="M9" s="2" t="inlineStr">
         <is>
-          <t>17589</t>
+          <t>16943</t>
         </is>
       </c>
       <c r="N9" s="2" t="inlineStr">
@@ -1351,12 +1351,12 @@
       </c>
       <c r="O9" s="2" t="inlineStr">
         <is>
-          <t>6,64%</t>
+          <t>6,78%</t>
         </is>
       </c>
       <c r="P9" s="2" t="inlineStr">
         <is>
-          <t>16,37%</t>
+          <t>15,77%</t>
         </is>
       </c>
       <c r="Q9" s="2" t="inlineStr">
@@ -1371,12 +1371,12 @@
       </c>
       <c r="S9" s="2" t="inlineStr">
         <is>
-          <t>17178</t>
+          <t>17959</t>
         </is>
       </c>
       <c r="T9" s="2" t="inlineStr">
         <is>
-          <t>32922</t>
+          <t>32257</t>
         </is>
       </c>
       <c r="U9" s="2" t="inlineStr">
@@ -1386,12 +1386,12 @@
       </c>
       <c r="V9" s="2" t="inlineStr">
         <is>
-          <t>8,22%</t>
+          <t>8,59%</t>
         </is>
       </c>
       <c r="W9" s="2" t="inlineStr">
         <is>
-          <t>15,75%</t>
+          <t>15,43%</t>
         </is>
       </c>
     </row>
@@ -1414,12 +1414,12 @@
       </c>
       <c r="E10" s="2" t="inlineStr">
         <is>
-          <t>45101</t>
+          <t>45757</t>
         </is>
       </c>
       <c r="F10" s="2" t="inlineStr">
         <is>
-          <t>61921</t>
+          <t>61997</t>
         </is>
       </c>
       <c r="G10" s="2" t="inlineStr">
@@ -1429,12 +1429,12 @@
       </c>
       <c r="H10" s="2" t="inlineStr">
         <is>
-          <t>44,41%</t>
+          <t>45,05%</t>
         </is>
       </c>
       <c r="I10" s="2" t="inlineStr">
         <is>
-          <t>60,97%</t>
+          <t>61,04%</t>
         </is>
       </c>
       <c r="J10" s="2" t="inlineStr">
@@ -1449,12 +1449,12 @@
       </c>
       <c r="L10" s="2" t="inlineStr">
         <is>
-          <t>53864</t>
+          <t>54637</t>
         </is>
       </c>
       <c r="M10" s="2" t="inlineStr">
         <is>
-          <t>70272</t>
+          <t>70812</t>
         </is>
       </c>
       <c r="N10" s="2" t="inlineStr">
@@ -1464,12 +1464,12 @@
       </c>
       <c r="O10" s="2" t="inlineStr">
         <is>
-          <t>50,12%</t>
+          <t>50,84%</t>
         </is>
       </c>
       <c r="P10" s="2" t="inlineStr">
         <is>
-          <t>65,39%</t>
+          <t>65,89%</t>
         </is>
       </c>
       <c r="Q10" s="2" t="inlineStr">
@@ -1484,12 +1484,12 @@
       </c>
       <c r="S10" s="2" t="inlineStr">
         <is>
-          <t>105078</t>
+          <t>105495</t>
         </is>
       </c>
       <c r="T10" s="2" t="inlineStr">
         <is>
-          <t>127442</t>
+          <t>127925</t>
         </is>
       </c>
       <c r="U10" s="2" t="inlineStr">
@@ -1499,12 +1499,12 @@
       </c>
       <c r="V10" s="2" t="inlineStr">
         <is>
-          <t>50,27%</t>
+          <t>50,47%</t>
         </is>
       </c>
       <c r="W10" s="2" t="inlineStr">
         <is>
-          <t>60,97%</t>
+          <t>61,2%</t>
         </is>
       </c>
     </row>
@@ -1644,12 +1644,12 @@
       </c>
       <c r="E12" s="2" t="inlineStr">
         <is>
-          <t>9098</t>
+          <t>9101</t>
         </is>
       </c>
       <c r="F12" s="2" t="inlineStr">
         <is>
-          <t>20348</t>
+          <t>19638</t>
         </is>
       </c>
       <c r="G12" s="2" t="inlineStr">
@@ -1659,12 +1659,12 @@
       </c>
       <c r="H12" s="2" t="inlineStr">
         <is>
-          <t>14,39%</t>
+          <t>14,4%</t>
         </is>
       </c>
       <c r="I12" s="2" t="inlineStr">
         <is>
-          <t>32,19%</t>
+          <t>31,07%</t>
         </is>
       </c>
       <c r="J12" s="2" t="inlineStr">
@@ -1679,12 +1679,12 @@
       </c>
       <c r="L12" s="2" t="inlineStr">
         <is>
-          <t>9111</t>
+          <t>8115</t>
         </is>
       </c>
       <c r="M12" s="2" t="inlineStr">
         <is>
-          <t>18600</t>
+          <t>17956</t>
         </is>
       </c>
       <c r="N12" s="2" t="inlineStr">
@@ -1694,12 +1694,12 @@
       </c>
       <c r="O12" s="2" t="inlineStr">
         <is>
-          <t>13,31%</t>
+          <t>11,86%</t>
         </is>
       </c>
       <c r="P12" s="2" t="inlineStr">
         <is>
-          <t>27,18%</t>
+          <t>26,24%</t>
         </is>
       </c>
       <c r="Q12" s="2" t="inlineStr">
@@ -1714,12 +1714,12 @@
       </c>
       <c r="S12" s="2" t="inlineStr">
         <is>
-          <t>19726</t>
+          <t>19832</t>
         </is>
       </c>
       <c r="T12" s="2" t="inlineStr">
         <is>
-          <t>35229</t>
+          <t>34536</t>
         </is>
       </c>
       <c r="U12" s="2" t="inlineStr">
@@ -1729,12 +1729,12 @@
       </c>
       <c r="V12" s="2" t="inlineStr">
         <is>
-          <t>14,99%</t>
+          <t>15,07%</t>
         </is>
       </c>
       <c r="W12" s="2" t="inlineStr">
         <is>
-          <t>26,76%</t>
+          <t>26,24%</t>
         </is>
       </c>
     </row>
@@ -1757,12 +1757,12 @@
       </c>
       <c r="E13" s="2" t="inlineStr">
         <is>
-          <t>2247</t>
+          <t>2223</t>
         </is>
       </c>
       <c r="F13" s="2" t="inlineStr">
         <is>
-          <t>10198</t>
+          <t>10235</t>
         </is>
       </c>
       <c r="G13" s="2" t="inlineStr">
@@ -1772,12 +1772,12 @@
       </c>
       <c r="H13" s="2" t="inlineStr">
         <is>
-          <t>3,55%</t>
+          <t>3,52%</t>
         </is>
       </c>
       <c r="I13" s="2" t="inlineStr">
         <is>
-          <t>16,13%</t>
+          <t>16,19%</t>
         </is>
       </c>
       <c r="J13" s="2" t="inlineStr">
@@ -1792,12 +1792,12 @@
       </c>
       <c r="L13" s="2" t="inlineStr">
         <is>
-          <t>5017</t>
+          <t>5054</t>
         </is>
       </c>
       <c r="M13" s="2" t="inlineStr">
         <is>
-          <t>13677</t>
+          <t>13820</t>
         </is>
       </c>
       <c r="N13" s="2" t="inlineStr">
@@ -1807,12 +1807,12 @@
       </c>
       <c r="O13" s="2" t="inlineStr">
         <is>
-          <t>7,33%</t>
+          <t>7,39%</t>
         </is>
       </c>
       <c r="P13" s="2" t="inlineStr">
         <is>
-          <t>19,99%</t>
+          <t>20,2%</t>
         </is>
       </c>
       <c r="Q13" s="2" t="inlineStr">
@@ -1827,12 +1827,12 @@
       </c>
       <c r="S13" s="2" t="inlineStr">
         <is>
-          <t>9349</t>
+          <t>9305</t>
         </is>
       </c>
       <c r="T13" s="2" t="inlineStr">
         <is>
-          <t>20798</t>
+          <t>20471</t>
         </is>
       </c>
       <c r="U13" s="2" t="inlineStr">
@@ -1842,12 +1842,12 @@
       </c>
       <c r="V13" s="2" t="inlineStr">
         <is>
-          <t>7,1%</t>
+          <t>7,07%</t>
         </is>
       </c>
       <c r="W13" s="2" t="inlineStr">
         <is>
-          <t>15,8%</t>
+          <t>15,55%</t>
         </is>
       </c>
     </row>
@@ -1870,12 +1870,12 @@
       </c>
       <c r="E14" s="2" t="inlineStr">
         <is>
-          <t>37565</t>
+          <t>38329</t>
         </is>
       </c>
       <c r="F14" s="2" t="inlineStr">
         <is>
-          <t>49617</t>
+          <t>49770</t>
         </is>
       </c>
       <c r="G14" s="2" t="inlineStr">
@@ -1885,12 +1885,12 @@
       </c>
       <c r="H14" s="2" t="inlineStr">
         <is>
-          <t>59,44%</t>
+          <t>60,64%</t>
         </is>
       </c>
       <c r="I14" s="2" t="inlineStr">
         <is>
-          <t>78,5%</t>
+          <t>78,75%</t>
         </is>
       </c>
       <c r="J14" s="2" t="inlineStr">
@@ -1905,12 +1905,12 @@
       </c>
       <c r="L14" s="2" t="inlineStr">
         <is>
-          <t>40372</t>
+          <t>40487</t>
         </is>
       </c>
       <c r="M14" s="2" t="inlineStr">
         <is>
-          <t>51959</t>
+          <t>52077</t>
         </is>
       </c>
       <c r="N14" s="2" t="inlineStr">
@@ -1920,12 +1920,12 @@
       </c>
       <c r="O14" s="2" t="inlineStr">
         <is>
-          <t>59,0%</t>
+          <t>59,16%</t>
         </is>
       </c>
       <c r="P14" s="2" t="inlineStr">
         <is>
-          <t>75,93%</t>
+          <t>76,1%</t>
         </is>
       </c>
       <c r="Q14" s="2" t="inlineStr">
@@ -1940,12 +1940,12 @@
       </c>
       <c r="S14" s="2" t="inlineStr">
         <is>
-          <t>81338</t>
+          <t>82121</t>
         </is>
       </c>
       <c r="T14" s="2" t="inlineStr">
         <is>
-          <t>98943</t>
+          <t>98906</t>
         </is>
       </c>
       <c r="U14" s="2" t="inlineStr">
@@ -1955,12 +1955,12 @@
       </c>
       <c r="V14" s="2" t="inlineStr">
         <is>
-          <t>61,79%</t>
+          <t>62,39%</t>
         </is>
       </c>
       <c r="W14" s="2" t="inlineStr">
         <is>
-          <t>75,17%</t>
+          <t>75,14%</t>
         </is>
       </c>
     </row>
@@ -2100,12 +2100,12 @@
       </c>
       <c r="E16" s="2" t="inlineStr">
         <is>
-          <t>6848</t>
+          <t>6455</t>
         </is>
       </c>
       <c r="F16" s="2" t="inlineStr">
         <is>
-          <t>16937</t>
+          <t>16782</t>
         </is>
       </c>
       <c r="G16" s="2" t="inlineStr">
@@ -2115,12 +2115,12 @@
       </c>
       <c r="H16" s="2" t="inlineStr">
         <is>
-          <t>9,23%</t>
+          <t>8,7%</t>
         </is>
       </c>
       <c r="I16" s="2" t="inlineStr">
         <is>
-          <t>22,82%</t>
+          <t>22,61%</t>
         </is>
       </c>
       <c r="J16" s="2" t="inlineStr">
@@ -2135,12 +2135,12 @@
       </c>
       <c r="L16" s="2" t="inlineStr">
         <is>
-          <t>11994</t>
+          <t>12217</t>
         </is>
       </c>
       <c r="M16" s="2" t="inlineStr">
         <is>
-          <t>24046</t>
+          <t>24286</t>
         </is>
       </c>
       <c r="N16" s="2" t="inlineStr">
@@ -2150,12 +2150,12 @@
       </c>
       <c r="O16" s="2" t="inlineStr">
         <is>
-          <t>15,32%</t>
+          <t>15,6%</t>
         </is>
       </c>
       <c r="P16" s="2" t="inlineStr">
         <is>
-          <t>30,71%</t>
+          <t>31,02%</t>
         </is>
       </c>
       <c r="Q16" s="2" t="inlineStr">
@@ -2170,12 +2170,12 @@
       </c>
       <c r="S16" s="2" t="inlineStr">
         <is>
-          <t>21526</t>
+          <t>21441</t>
         </is>
       </c>
       <c r="T16" s="2" t="inlineStr">
         <is>
-          <t>36721</t>
+          <t>36243</t>
         </is>
       </c>
       <c r="U16" s="2" t="inlineStr">
@@ -2185,12 +2185,12 @@
       </c>
       <c r="V16" s="2" t="inlineStr">
         <is>
-          <t>14,11%</t>
+          <t>14,06%</t>
         </is>
       </c>
       <c r="W16" s="2" t="inlineStr">
         <is>
-          <t>24,07%</t>
+          <t>23,76%</t>
         </is>
       </c>
     </row>
@@ -2213,12 +2213,12 @@
       </c>
       <c r="E17" s="2" t="inlineStr">
         <is>
-          <t>7164</t>
+          <t>7148</t>
         </is>
       </c>
       <c r="F17" s="2" t="inlineStr">
         <is>
-          <t>16168</t>
+          <t>17080</t>
         </is>
       </c>
       <c r="G17" s="2" t="inlineStr">
@@ -2228,12 +2228,12 @@
       </c>
       <c r="H17" s="2" t="inlineStr">
         <is>
-          <t>9,65%</t>
+          <t>9,63%</t>
         </is>
       </c>
       <c r="I17" s="2" t="inlineStr">
         <is>
-          <t>21,78%</t>
+          <t>23,01%</t>
         </is>
       </c>
       <c r="J17" s="2" t="inlineStr">
@@ -2248,12 +2248,12 @@
       </c>
       <c r="L17" s="2" t="inlineStr">
         <is>
-          <t>8864</t>
+          <t>9648</t>
         </is>
       </c>
       <c r="M17" s="2" t="inlineStr">
         <is>
-          <t>20120</t>
+          <t>20667</t>
         </is>
       </c>
       <c r="N17" s="2" t="inlineStr">
@@ -2263,12 +2263,12 @@
       </c>
       <c r="O17" s="2" t="inlineStr">
         <is>
-          <t>11,32%</t>
+          <t>12,32%</t>
         </is>
       </c>
       <c r="P17" s="2" t="inlineStr">
         <is>
-          <t>25,7%</t>
+          <t>26,4%</t>
         </is>
       </c>
       <c r="Q17" s="2" t="inlineStr">
@@ -2283,12 +2283,12 @@
       </c>
       <c r="S17" s="2" t="inlineStr">
         <is>
-          <t>18762</t>
+          <t>19438</t>
         </is>
       </c>
       <c r="T17" s="2" t="inlineStr">
         <is>
-          <t>33806</t>
+          <t>34141</t>
         </is>
       </c>
       <c r="U17" s="2" t="inlineStr">
@@ -2298,12 +2298,12 @@
       </c>
       <c r="V17" s="2" t="inlineStr">
         <is>
-          <t>12,3%</t>
+          <t>12,74%</t>
         </is>
       </c>
       <c r="W17" s="2" t="inlineStr">
         <is>
-          <t>22,16%</t>
+          <t>22,38%</t>
         </is>
       </c>
     </row>
@@ -2326,12 +2326,12 @@
       </c>
       <c r="E18" s="2" t="inlineStr">
         <is>
-          <t>44609</t>
+          <t>44994</t>
         </is>
       </c>
       <c r="F18" s="2" t="inlineStr">
         <is>
-          <t>57416</t>
+          <t>58663</t>
         </is>
       </c>
       <c r="G18" s="2" t="inlineStr">
@@ -2341,12 +2341,12 @@
       </c>
       <c r="H18" s="2" t="inlineStr">
         <is>
-          <t>60,09%</t>
+          <t>60,61%</t>
         </is>
       </c>
       <c r="I18" s="2" t="inlineStr">
         <is>
-          <t>77,34%</t>
+          <t>79,02%</t>
         </is>
       </c>
       <c r="J18" s="2" t="inlineStr">
@@ -2361,12 +2361,12 @@
       </c>
       <c r="L18" s="2" t="inlineStr">
         <is>
-          <t>38862</t>
+          <t>39160</t>
         </is>
       </c>
       <c r="M18" s="2" t="inlineStr">
         <is>
-          <t>53509</t>
+          <t>53232</t>
         </is>
       </c>
       <c r="N18" s="2" t="inlineStr">
@@ -2376,12 +2376,12 @@
       </c>
       <c r="O18" s="2" t="inlineStr">
         <is>
-          <t>49,63%</t>
+          <t>50,01%</t>
         </is>
       </c>
       <c r="P18" s="2" t="inlineStr">
         <is>
-          <t>68,34%</t>
+          <t>67,99%</t>
         </is>
       </c>
       <c r="Q18" s="2" t="inlineStr">
@@ -2396,12 +2396,12 @@
       </c>
       <c r="S18" s="2" t="inlineStr">
         <is>
-          <t>88347</t>
+          <t>88035</t>
         </is>
       </c>
       <c r="T18" s="2" t="inlineStr">
         <is>
-          <t>107689</t>
+          <t>107584</t>
         </is>
       </c>
       <c r="U18" s="2" t="inlineStr">
@@ -2411,12 +2411,12 @@
       </c>
       <c r="V18" s="2" t="inlineStr">
         <is>
-          <t>57,92%</t>
+          <t>57,72%</t>
         </is>
       </c>
       <c r="W18" s="2" t="inlineStr">
         <is>
-          <t>70,6%</t>
+          <t>70,53%</t>
         </is>
       </c>
     </row>
@@ -2556,12 +2556,12 @@
       </c>
       <c r="E20" s="2" t="inlineStr">
         <is>
-          <t>10283</t>
+          <t>10425</t>
         </is>
       </c>
       <c r="F20" s="2" t="inlineStr">
         <is>
-          <t>19643</t>
+          <t>20303</t>
         </is>
       </c>
       <c r="G20" s="2" t="inlineStr">
@@ -2571,12 +2571,12 @@
       </c>
       <c r="H20" s="2" t="inlineStr">
         <is>
-          <t>24,94%</t>
+          <t>25,29%</t>
         </is>
       </c>
       <c r="I20" s="2" t="inlineStr">
         <is>
-          <t>47,64%</t>
+          <t>49,24%</t>
         </is>
       </c>
       <c r="J20" s="2" t="inlineStr">
@@ -2591,12 +2591,12 @@
       </c>
       <c r="L20" s="2" t="inlineStr">
         <is>
-          <t>10580</t>
+          <t>10563</t>
         </is>
       </c>
       <c r="M20" s="2" t="inlineStr">
         <is>
-          <t>21174</t>
+          <t>20544</t>
         </is>
       </c>
       <c r="N20" s="2" t="inlineStr">
@@ -2606,12 +2606,12 @@
       </c>
       <c r="O20" s="2" t="inlineStr">
         <is>
-          <t>23,59%</t>
+          <t>23,55%</t>
         </is>
       </c>
       <c r="P20" s="2" t="inlineStr">
         <is>
-          <t>47,22%</t>
+          <t>45,81%</t>
         </is>
       </c>
       <c r="Q20" s="2" t="inlineStr">
@@ -2626,12 +2626,12 @@
       </c>
       <c r="S20" s="2" t="inlineStr">
         <is>
-          <t>23572</t>
+          <t>22645</t>
         </is>
       </c>
       <c r="T20" s="2" t="inlineStr">
         <is>
-          <t>37763</t>
+          <t>37560</t>
         </is>
       </c>
       <c r="U20" s="2" t="inlineStr">
@@ -2641,12 +2641,12 @@
       </c>
       <c r="V20" s="2" t="inlineStr">
         <is>
-          <t>27,39%</t>
+          <t>26,31%</t>
         </is>
       </c>
       <c r="W20" s="2" t="inlineStr">
         <is>
-          <t>43,87%</t>
+          <t>43,64%</t>
         </is>
       </c>
     </row>
@@ -2669,12 +2669,12 @@
       </c>
       <c r="E21" s="2" t="inlineStr">
         <is>
-          <t>2778</t>
+          <t>2921</t>
         </is>
       </c>
       <c r="F21" s="2" t="inlineStr">
         <is>
-          <t>10678</t>
+          <t>10436</t>
         </is>
       </c>
       <c r="G21" s="2" t="inlineStr">
@@ -2684,12 +2684,12 @@
       </c>
       <c r="H21" s="2" t="inlineStr">
         <is>
-          <t>6,74%</t>
+          <t>7,09%</t>
         </is>
       </c>
       <c r="I21" s="2" t="inlineStr">
         <is>
-          <t>25,9%</t>
+          <t>25,31%</t>
         </is>
       </c>
       <c r="J21" s="2" t="inlineStr">
@@ -2704,12 +2704,12 @@
       </c>
       <c r="L21" s="2" t="inlineStr">
         <is>
-          <t>3396</t>
+          <t>2819</t>
         </is>
       </c>
       <c r="M21" s="2" t="inlineStr">
         <is>
-          <t>10602</t>
+          <t>10575</t>
         </is>
       </c>
       <c r="N21" s="2" t="inlineStr">
@@ -2719,12 +2719,12 @@
       </c>
       <c r="O21" s="2" t="inlineStr">
         <is>
-          <t>7,57%</t>
+          <t>6,29%</t>
         </is>
       </c>
       <c r="P21" s="2" t="inlineStr">
         <is>
-          <t>23,64%</t>
+          <t>23,58%</t>
         </is>
       </c>
       <c r="Q21" s="2" t="inlineStr">
@@ -2739,12 +2739,12 @@
       </c>
       <c r="S21" s="2" t="inlineStr">
         <is>
-          <t>7285</t>
+          <t>7235</t>
         </is>
       </c>
       <c r="T21" s="2" t="inlineStr">
         <is>
-          <t>18279</t>
+          <t>18130</t>
         </is>
       </c>
       <c r="U21" s="2" t="inlineStr">
@@ -2754,12 +2754,12 @@
       </c>
       <c r="V21" s="2" t="inlineStr">
         <is>
-          <t>8,46%</t>
+          <t>8,41%</t>
         </is>
       </c>
       <c r="W21" s="2" t="inlineStr">
         <is>
-          <t>21,24%</t>
+          <t>21,06%</t>
         </is>
       </c>
     </row>
@@ -2782,12 +2782,12 @@
       </c>
       <c r="E22" s="2" t="inlineStr">
         <is>
-          <t>14398</t>
+          <t>15078</t>
         </is>
       </c>
       <c r="F22" s="2" t="inlineStr">
         <is>
-          <t>25157</t>
+          <t>25517</t>
         </is>
       </c>
       <c r="G22" s="2" t="inlineStr">
@@ -2797,12 +2797,12 @@
       </c>
       <c r="H22" s="2" t="inlineStr">
         <is>
-          <t>34,92%</t>
+          <t>36,57%</t>
         </is>
       </c>
       <c r="I22" s="2" t="inlineStr">
         <is>
-          <t>61,02%</t>
+          <t>61,89%</t>
         </is>
       </c>
       <c r="J22" s="2" t="inlineStr">
@@ -2817,12 +2817,12 @@
       </c>
       <c r="L22" s="2" t="inlineStr">
         <is>
-          <t>17572</t>
+          <t>17921</t>
         </is>
       </c>
       <c r="M22" s="2" t="inlineStr">
         <is>
-          <t>28554</t>
+          <t>28712</t>
         </is>
       </c>
       <c r="N22" s="2" t="inlineStr">
@@ -2832,12 +2832,12 @@
       </c>
       <c r="O22" s="2" t="inlineStr">
         <is>
-          <t>39,19%</t>
+          <t>39,96%</t>
         </is>
       </c>
       <c r="P22" s="2" t="inlineStr">
         <is>
-          <t>63,67%</t>
+          <t>64,03%</t>
         </is>
       </c>
       <c r="Q22" s="2" t="inlineStr">
@@ -2852,12 +2852,12 @@
       </c>
       <c r="S22" s="2" t="inlineStr">
         <is>
-          <t>35396</t>
+          <t>36345</t>
         </is>
       </c>
       <c r="T22" s="2" t="inlineStr">
         <is>
-          <t>50361</t>
+          <t>51396</t>
         </is>
       </c>
       <c r="U22" s="2" t="inlineStr">
@@ -2867,12 +2867,12 @@
       </c>
       <c r="V22" s="2" t="inlineStr">
         <is>
-          <t>41,12%</t>
+          <t>42,23%</t>
         </is>
       </c>
       <c r="W22" s="2" t="inlineStr">
         <is>
-          <t>58,51%</t>
+          <t>59,71%</t>
         </is>
       </c>
     </row>
@@ -3012,12 +3012,12 @@
       </c>
       <c r="E24" s="2" t="inlineStr">
         <is>
-          <t>3927</t>
+          <t>3929</t>
         </is>
       </c>
       <c r="F24" s="2" t="inlineStr">
         <is>
-          <t>11930</t>
+          <t>11745</t>
         </is>
       </c>
       <c r="G24" s="2" t="inlineStr">
@@ -3032,7 +3032,7 @@
       </c>
       <c r="I24" s="2" t="inlineStr">
         <is>
-          <t>21,83%</t>
+          <t>21,49%</t>
         </is>
       </c>
       <c r="J24" s="2" t="inlineStr">
@@ -3047,12 +3047,12 @@
       </c>
       <c r="L24" s="2" t="inlineStr">
         <is>
-          <t>5697</t>
+          <t>6245</t>
         </is>
       </c>
       <c r="M24" s="2" t="inlineStr">
         <is>
-          <t>14811</t>
+          <t>15627</t>
         </is>
       </c>
       <c r="N24" s="2" t="inlineStr">
@@ -3062,12 +3062,12 @@
       </c>
       <c r="O24" s="2" t="inlineStr">
         <is>
-          <t>9,86%</t>
+          <t>10,81%</t>
         </is>
       </c>
       <c r="P24" s="2" t="inlineStr">
         <is>
-          <t>25,64%</t>
+          <t>27,05%</t>
         </is>
       </c>
       <c r="Q24" s="2" t="inlineStr">
@@ -3082,12 +3082,12 @@
       </c>
       <c r="S24" s="2" t="inlineStr">
         <is>
-          <t>12264</t>
+          <t>11730</t>
         </is>
       </c>
       <c r="T24" s="2" t="inlineStr">
         <is>
-          <t>24623</t>
+          <t>23968</t>
         </is>
       </c>
       <c r="U24" s="2" t="inlineStr">
@@ -3097,12 +3097,12 @@
       </c>
       <c r="V24" s="2" t="inlineStr">
         <is>
-          <t>10,91%</t>
+          <t>10,43%</t>
         </is>
       </c>
       <c r="W24" s="2" t="inlineStr">
         <is>
-          <t>21,9%</t>
+          <t>21,32%</t>
         </is>
       </c>
     </row>
@@ -3125,12 +3125,12 @@
       </c>
       <c r="E25" s="2" t="inlineStr">
         <is>
-          <t>1342</t>
+          <t>1790</t>
         </is>
       </c>
       <c r="F25" s="2" t="inlineStr">
         <is>
-          <t>8040</t>
+          <t>8010</t>
         </is>
       </c>
       <c r="G25" s="2" t="inlineStr">
@@ -3140,12 +3140,12 @@
       </c>
       <c r="H25" s="2" t="inlineStr">
         <is>
-          <t>2,46%</t>
+          <t>3,28%</t>
         </is>
       </c>
       <c r="I25" s="2" t="inlineStr">
         <is>
-          <t>14,71%</t>
+          <t>14,66%</t>
         </is>
       </c>
       <c r="J25" s="2" t="inlineStr">
@@ -3160,12 +3160,12 @@
       </c>
       <c r="L25" s="2" t="inlineStr">
         <is>
-          <t>1340</t>
+          <t>1281</t>
         </is>
       </c>
       <c r="M25" s="2" t="inlineStr">
         <is>
-          <t>7550</t>
+          <t>7538</t>
         </is>
       </c>
       <c r="N25" s="2" t="inlineStr">
@@ -3175,12 +3175,12 @@
       </c>
       <c r="O25" s="2" t="inlineStr">
         <is>
-          <t>2,32%</t>
+          <t>2,22%</t>
         </is>
       </c>
       <c r="P25" s="2" t="inlineStr">
         <is>
-          <t>13,07%</t>
+          <t>13,05%</t>
         </is>
       </c>
       <c r="Q25" s="2" t="inlineStr">
@@ -3195,12 +3195,12 @@
       </c>
       <c r="S25" s="2" t="inlineStr">
         <is>
-          <t>3966</t>
+          <t>4398</t>
         </is>
       </c>
       <c r="T25" s="2" t="inlineStr">
         <is>
-          <t>12877</t>
+          <t>12963</t>
         </is>
       </c>
       <c r="U25" s="2" t="inlineStr">
@@ -3210,12 +3210,12 @@
       </c>
       <c r="V25" s="2" t="inlineStr">
         <is>
-          <t>3,53%</t>
+          <t>3,91%</t>
         </is>
       </c>
       <c r="W25" s="2" t="inlineStr">
         <is>
-          <t>11,45%</t>
+          <t>11,53%</t>
         </is>
       </c>
     </row>
@@ -3238,12 +3238,12 @@
       </c>
       <c r="E26" s="2" t="inlineStr">
         <is>
-          <t>37792</t>
+          <t>37988</t>
         </is>
       </c>
       <c r="F26" s="2" t="inlineStr">
         <is>
-          <t>47382</t>
+          <t>47390</t>
         </is>
       </c>
       <c r="G26" s="2" t="inlineStr">
@@ -3253,12 +3253,12 @@
       </c>
       <c r="H26" s="2" t="inlineStr">
         <is>
-          <t>69,15%</t>
+          <t>69,51%</t>
         </is>
       </c>
       <c r="I26" s="2" t="inlineStr">
         <is>
-          <t>86,7%</t>
+          <t>86,72%</t>
         </is>
       </c>
       <c r="J26" s="2" t="inlineStr">
@@ -3273,12 +3273,12 @@
       </c>
       <c r="L26" s="2" t="inlineStr">
         <is>
-          <t>38444</t>
+          <t>38105</t>
         </is>
       </c>
       <c r="M26" s="2" t="inlineStr">
         <is>
-          <t>48901</t>
+          <t>48549</t>
         </is>
       </c>
       <c r="N26" s="2" t="inlineStr">
@@ -3288,12 +3288,12 @@
       </c>
       <c r="O26" s="2" t="inlineStr">
         <is>
-          <t>66,55%</t>
+          <t>65,96%</t>
         </is>
       </c>
       <c r="P26" s="2" t="inlineStr">
         <is>
-          <t>84,65%</t>
+          <t>84,04%</t>
         </is>
       </c>
       <c r="Q26" s="2" t="inlineStr">
@@ -3308,12 +3308,12 @@
       </c>
       <c r="S26" s="2" t="inlineStr">
         <is>
-          <t>79824</t>
+          <t>80329</t>
         </is>
       </c>
       <c r="T26" s="2" t="inlineStr">
         <is>
-          <t>93727</t>
+          <t>93970</t>
         </is>
       </c>
       <c r="U26" s="2" t="inlineStr">
@@ -3323,12 +3323,12 @@
       </c>
       <c r="V26" s="2" t="inlineStr">
         <is>
-          <t>71,01%</t>
+          <t>71,45%</t>
         </is>
       </c>
       <c r="W26" s="2" t="inlineStr">
         <is>
-          <t>83,37%</t>
+          <t>83,59%</t>
         </is>
       </c>
     </row>
@@ -3468,12 +3468,12 @@
       </c>
       <c r="E28" s="2" t="inlineStr">
         <is>
-          <t>17065</t>
+          <t>16648</t>
         </is>
       </c>
       <c r="F28" s="2" t="inlineStr">
         <is>
-          <t>31043</t>
+          <t>30816</t>
         </is>
       </c>
       <c r="G28" s="2" t="inlineStr">
@@ -3483,12 +3483,12 @@
       </c>
       <c r="H28" s="2" t="inlineStr">
         <is>
-          <t>13,56%</t>
+          <t>13,23%</t>
         </is>
       </c>
       <c r="I28" s="2" t="inlineStr">
         <is>
-          <t>24,67%</t>
+          <t>24,49%</t>
         </is>
       </c>
       <c r="J28" s="2" t="inlineStr">
@@ -3503,12 +3503,12 @@
       </c>
       <c r="L28" s="2" t="inlineStr">
         <is>
-          <t>22317</t>
+          <t>22473</t>
         </is>
       </c>
       <c r="M28" s="2" t="inlineStr">
         <is>
-          <t>37267</t>
+          <t>37038</t>
         </is>
       </c>
       <c r="N28" s="2" t="inlineStr">
@@ -3518,12 +3518,12 @@
       </c>
       <c r="O28" s="2" t="inlineStr">
         <is>
-          <t>17,44%</t>
+          <t>17,56%</t>
         </is>
       </c>
       <c r="P28" s="2" t="inlineStr">
         <is>
-          <t>29,12%</t>
+          <t>28,94%</t>
         </is>
       </c>
       <c r="Q28" s="2" t="inlineStr">
@@ -3538,12 +3538,12 @@
       </c>
       <c r="S28" s="2" t="inlineStr">
         <is>
-          <t>42680</t>
+          <t>43283</t>
         </is>
       </c>
       <c r="T28" s="2" t="inlineStr">
         <is>
-          <t>64213</t>
+          <t>64709</t>
         </is>
       </c>
       <c r="U28" s="2" t="inlineStr">
@@ -3553,12 +3553,12 @@
       </c>
       <c r="V28" s="2" t="inlineStr">
         <is>
-          <t>16,81%</t>
+          <t>17,05%</t>
         </is>
       </c>
       <c r="W28" s="2" t="inlineStr">
         <is>
-          <t>25,3%</t>
+          <t>25,49%</t>
         </is>
       </c>
     </row>
@@ -3581,12 +3581,12 @@
       </c>
       <c r="E29" s="2" t="inlineStr">
         <is>
-          <t>4751</t>
+          <t>5321</t>
         </is>
       </c>
       <c r="F29" s="2" t="inlineStr">
         <is>
-          <t>14009</t>
+          <t>15067</t>
         </is>
       </c>
       <c r="G29" s="2" t="inlineStr">
@@ -3596,12 +3596,12 @@
       </c>
       <c r="H29" s="2" t="inlineStr">
         <is>
-          <t>3,78%</t>
+          <t>4,23%</t>
         </is>
       </c>
       <c r="I29" s="2" t="inlineStr">
         <is>
-          <t>11,13%</t>
+          <t>11,97%</t>
         </is>
       </c>
       <c r="J29" s="2" t="inlineStr">
@@ -3616,12 +3616,12 @@
       </c>
       <c r="L29" s="2" t="inlineStr">
         <is>
-          <t>8502</t>
+          <t>8460</t>
         </is>
       </c>
       <c r="M29" s="2" t="inlineStr">
         <is>
-          <t>20476</t>
+          <t>19911</t>
         </is>
       </c>
       <c r="N29" s="2" t="inlineStr">
@@ -3631,12 +3631,12 @@
       </c>
       <c r="O29" s="2" t="inlineStr">
         <is>
-          <t>6,64%</t>
+          <t>6,61%</t>
         </is>
       </c>
       <c r="P29" s="2" t="inlineStr">
         <is>
-          <t>16,0%</t>
+          <t>15,56%</t>
         </is>
       </c>
       <c r="Q29" s="2" t="inlineStr">
@@ -3651,12 +3651,12 @@
       </c>
       <c r="S29" s="2" t="inlineStr">
         <is>
-          <t>16014</t>
+          <t>15926</t>
         </is>
       </c>
       <c r="T29" s="2" t="inlineStr">
         <is>
-          <t>31002</t>
+          <t>30793</t>
         </is>
       </c>
       <c r="U29" s="2" t="inlineStr">
@@ -3666,12 +3666,12 @@
       </c>
       <c r="V29" s="2" t="inlineStr">
         <is>
-          <t>6,31%</t>
+          <t>6,27%</t>
         </is>
       </c>
       <c r="W29" s="2" t="inlineStr">
         <is>
-          <t>12,21%</t>
+          <t>12,13%</t>
         </is>
       </c>
     </row>
@@ -3694,12 +3694,12 @@
       </c>
       <c r="E30" s="2" t="inlineStr">
         <is>
-          <t>85166</t>
+          <t>85114</t>
         </is>
       </c>
       <c r="F30" s="2" t="inlineStr">
         <is>
-          <t>102040</t>
+          <t>100760</t>
         </is>
       </c>
       <c r="G30" s="2" t="inlineStr">
@@ -3709,12 +3709,12 @@
       </c>
       <c r="H30" s="2" t="inlineStr">
         <is>
-          <t>67,67%</t>
+          <t>67,63%</t>
         </is>
       </c>
       <c r="I30" s="2" t="inlineStr">
         <is>
-          <t>81,08%</t>
+          <t>80,06%</t>
         </is>
       </c>
       <c r="J30" s="2" t="inlineStr">
@@ -3729,12 +3729,12 @@
       </c>
       <c r="L30" s="2" t="inlineStr">
         <is>
-          <t>76080</t>
+          <t>75653</t>
         </is>
       </c>
       <c r="M30" s="2" t="inlineStr">
         <is>
-          <t>92640</t>
+          <t>93438</t>
         </is>
       </c>
       <c r="N30" s="2" t="inlineStr">
@@ -3744,12 +3744,12 @@
       </c>
       <c r="O30" s="2" t="inlineStr">
         <is>
-          <t>59,45%</t>
+          <t>59,12%</t>
         </is>
       </c>
       <c r="P30" s="2" t="inlineStr">
         <is>
-          <t>72,39%</t>
+          <t>73,01%</t>
         </is>
       </c>
       <c r="Q30" s="2" t="inlineStr">
@@ -3764,12 +3764,12 @@
       </c>
       <c r="S30" s="2" t="inlineStr">
         <is>
-          <t>165572</t>
+          <t>166008</t>
         </is>
       </c>
       <c r="T30" s="2" t="inlineStr">
         <is>
-          <t>189648</t>
+          <t>189506</t>
         </is>
       </c>
       <c r="U30" s="2" t="inlineStr">
@@ -3779,12 +3779,12 @@
       </c>
       <c r="V30" s="2" t="inlineStr">
         <is>
-          <t>65,23%</t>
+          <t>65,4%</t>
         </is>
       </c>
       <c r="W30" s="2" t="inlineStr">
         <is>
-          <t>74,71%</t>
+          <t>74,66%</t>
         </is>
       </c>
     </row>
@@ -3924,12 +3924,12 @@
       </c>
       <c r="E32" s="2" t="inlineStr">
         <is>
-          <t>37874</t>
+          <t>38590</t>
         </is>
       </c>
       <c r="F32" s="2" t="inlineStr">
         <is>
-          <t>55935</t>
+          <t>56521</t>
         </is>
       </c>
       <c r="G32" s="2" t="inlineStr">
@@ -3939,12 +3939,12 @@
       </c>
       <c r="H32" s="2" t="inlineStr">
         <is>
-          <t>25,0%</t>
+          <t>25,48%</t>
         </is>
       </c>
       <c r="I32" s="2" t="inlineStr">
         <is>
-          <t>36,93%</t>
+          <t>37,31%</t>
         </is>
       </c>
       <c r="J32" s="2" t="inlineStr">
@@ -3959,12 +3959,12 @@
       </c>
       <c r="L32" s="2" t="inlineStr">
         <is>
-          <t>37862</t>
+          <t>38308</t>
         </is>
       </c>
       <c r="M32" s="2" t="inlineStr">
         <is>
-          <t>55936</t>
+          <t>55920</t>
         </is>
       </c>
       <c r="N32" s="2" t="inlineStr">
@@ -3974,12 +3974,12 @@
       </c>
       <c r="O32" s="2" t="inlineStr">
         <is>
-          <t>23,98%</t>
+          <t>24,26%</t>
         </is>
       </c>
       <c r="P32" s="2" t="inlineStr">
         <is>
-          <t>35,43%</t>
+          <t>35,42%</t>
         </is>
       </c>
       <c r="Q32" s="2" t="inlineStr">
@@ -3994,12 +3994,12 @@
       </c>
       <c r="S32" s="2" t="inlineStr">
         <is>
-          <t>81095</t>
+          <t>81777</t>
         </is>
       </c>
       <c r="T32" s="2" t="inlineStr">
         <is>
-          <t>108130</t>
+          <t>107877</t>
         </is>
       </c>
       <c r="U32" s="2" t="inlineStr">
@@ -4009,12 +4009,12 @@
       </c>
       <c r="V32" s="2" t="inlineStr">
         <is>
-          <t>26,21%</t>
+          <t>26,43%</t>
         </is>
       </c>
       <c r="W32" s="2" t="inlineStr">
         <is>
-          <t>34,95%</t>
+          <t>34,87%</t>
         </is>
       </c>
     </row>
@@ -4037,12 +4037,12 @@
       </c>
       <c r="E33" s="2" t="inlineStr">
         <is>
-          <t>15494</t>
+          <t>14816</t>
         </is>
       </c>
       <c r="F33" s="2" t="inlineStr">
         <is>
-          <t>28771</t>
+          <t>28412</t>
         </is>
       </c>
       <c r="G33" s="2" t="inlineStr">
@@ -4052,12 +4052,12 @@
       </c>
       <c r="H33" s="2" t="inlineStr">
         <is>
-          <t>10,23%</t>
+          <t>9,78%</t>
         </is>
       </c>
       <c r="I33" s="2" t="inlineStr">
         <is>
-          <t>18,99%</t>
+          <t>18,76%</t>
         </is>
       </c>
       <c r="J33" s="2" t="inlineStr">
@@ -4072,12 +4072,12 @@
       </c>
       <c r="L33" s="2" t="inlineStr">
         <is>
-          <t>15211</t>
+          <t>16031</t>
         </is>
       </c>
       <c r="M33" s="2" t="inlineStr">
         <is>
-          <t>29453</t>
+          <t>29765</t>
         </is>
       </c>
       <c r="N33" s="2" t="inlineStr">
@@ -4087,12 +4087,12 @@
       </c>
       <c r="O33" s="2" t="inlineStr">
         <is>
-          <t>9,63%</t>
+          <t>10,15%</t>
         </is>
       </c>
       <c r="P33" s="2" t="inlineStr">
         <is>
-          <t>18,65%</t>
+          <t>18,85%</t>
         </is>
       </c>
       <c r="Q33" s="2" t="inlineStr">
@@ -4107,12 +4107,12 @@
       </c>
       <c r="S33" s="2" t="inlineStr">
         <is>
-          <t>34199</t>
+          <t>33045</t>
         </is>
       </c>
       <c r="T33" s="2" t="inlineStr">
         <is>
-          <t>53467</t>
+          <t>53327</t>
         </is>
       </c>
       <c r="U33" s="2" t="inlineStr">
@@ -4122,12 +4122,12 @@
       </c>
       <c r="V33" s="2" t="inlineStr">
         <is>
-          <t>11,05%</t>
+          <t>10,68%</t>
         </is>
       </c>
       <c r="W33" s="2" t="inlineStr">
         <is>
-          <t>17,28%</t>
+          <t>17,24%</t>
         </is>
       </c>
     </row>
@@ -4150,12 +4150,12 @@
       </c>
       <c r="E34" s="2" t="inlineStr">
         <is>
-          <t>74277</t>
+          <t>73424</t>
         </is>
       </c>
       <c r="F34" s="2" t="inlineStr">
         <is>
-          <t>92943</t>
+          <t>92476</t>
         </is>
       </c>
       <c r="G34" s="2" t="inlineStr">
@@ -4165,12 +4165,12 @@
       </c>
       <c r="H34" s="2" t="inlineStr">
         <is>
-          <t>49,03%</t>
+          <t>48,47%</t>
         </is>
       </c>
       <c r="I34" s="2" t="inlineStr">
         <is>
-          <t>61,36%</t>
+          <t>61,05%</t>
         </is>
       </c>
       <c r="J34" s="2" t="inlineStr">
@@ -4185,12 +4185,12 @@
       </c>
       <c r="L34" s="2" t="inlineStr">
         <is>
-          <t>79590</t>
+          <t>79456</t>
         </is>
       </c>
       <c r="M34" s="2" t="inlineStr">
         <is>
-          <t>98424</t>
+          <t>98789</t>
         </is>
       </c>
       <c r="N34" s="2" t="inlineStr">
@@ -4200,12 +4200,12 @@
       </c>
       <c r="O34" s="2" t="inlineStr">
         <is>
-          <t>50,41%</t>
+          <t>50,32%</t>
         </is>
       </c>
       <c r="P34" s="2" t="inlineStr">
         <is>
-          <t>62,34%</t>
+          <t>62,57%</t>
         </is>
       </c>
       <c r="Q34" s="2" t="inlineStr">
@@ -4220,12 +4220,12 @@
       </c>
       <c r="S34" s="2" t="inlineStr">
         <is>
-          <t>160505</t>
+          <t>157937</t>
         </is>
       </c>
       <c r="T34" s="2" t="inlineStr">
         <is>
-          <t>187053</t>
+          <t>186131</t>
         </is>
       </c>
       <c r="U34" s="2" t="inlineStr">
@@ -4235,12 +4235,12 @@
       </c>
       <c r="V34" s="2" t="inlineStr">
         <is>
-          <t>51,88%</t>
+          <t>51,05%</t>
         </is>
       </c>
       <c r="W34" s="2" t="inlineStr">
         <is>
-          <t>60,46%</t>
+          <t>60,16%</t>
         </is>
       </c>
     </row>
@@ -4380,12 +4380,12 @@
       </c>
       <c r="E36" s="2" t="inlineStr">
         <is>
-          <t>141074</t>
+          <t>142679</t>
         </is>
       </c>
       <c r="F36" s="2" t="inlineStr">
         <is>
-          <t>177498</t>
+          <t>177534</t>
         </is>
       </c>
       <c r="G36" s="2" t="inlineStr">
@@ -4395,12 +4395,12 @@
       </c>
       <c r="H36" s="2" t="inlineStr">
         <is>
-          <t>21,34%</t>
+          <t>21,59%</t>
         </is>
       </c>
       <c r="I36" s="2" t="inlineStr">
         <is>
-          <t>26,85%</t>
+          <t>26,86%</t>
         </is>
       </c>
       <c r="J36" s="2" t="inlineStr">
@@ -4415,12 +4415,12 @@
       </c>
       <c r="L36" s="2" t="inlineStr">
         <is>
-          <t>157117</t>
+          <t>158721</t>
         </is>
       </c>
       <c r="M36" s="2" t="inlineStr">
         <is>
-          <t>193258</t>
+          <t>195439</t>
         </is>
       </c>
       <c r="N36" s="2" t="inlineStr">
@@ -4430,12 +4430,12 @@
       </c>
       <c r="O36" s="2" t="inlineStr">
         <is>
-          <t>22,47%</t>
+          <t>22,7%</t>
         </is>
       </c>
       <c r="P36" s="2" t="inlineStr">
         <is>
-          <t>27,64%</t>
+          <t>27,95%</t>
         </is>
       </c>
       <c r="Q36" s="2" t="inlineStr">
@@ -4450,12 +4450,12 @@
       </c>
       <c r="S36" s="2" t="inlineStr">
         <is>
-          <t>310916</t>
+          <t>312500</t>
         </is>
       </c>
       <c r="T36" s="2" t="inlineStr">
         <is>
-          <t>361299</t>
+          <t>360328</t>
         </is>
       </c>
       <c r="U36" s="2" t="inlineStr">
@@ -4465,12 +4465,12 @@
       </c>
       <c r="V36" s="2" t="inlineStr">
         <is>
-          <t>22,86%</t>
+          <t>22,97%</t>
         </is>
       </c>
       <c r="W36" s="2" t="inlineStr">
         <is>
-          <t>26,56%</t>
+          <t>26,49%</t>
         </is>
       </c>
     </row>
@@ -4493,12 +4493,12 @@
       </c>
       <c r="E37" s="2" t="inlineStr">
         <is>
-          <t>66662</t>
+          <t>66446</t>
         </is>
       </c>
       <c r="F37" s="2" t="inlineStr">
         <is>
-          <t>90879</t>
+          <t>93239</t>
         </is>
       </c>
       <c r="G37" s="2" t="inlineStr">
@@ -4508,12 +4508,12 @@
       </c>
       <c r="H37" s="2" t="inlineStr">
         <is>
-          <t>10,08%</t>
+          <t>10,05%</t>
         </is>
       </c>
       <c r="I37" s="2" t="inlineStr">
         <is>
-          <t>13,75%</t>
+          <t>14,11%</t>
         </is>
       </c>
       <c r="J37" s="2" t="inlineStr">
@@ -4528,12 +4528,12 @@
       </c>
       <c r="L37" s="2" t="inlineStr">
         <is>
-          <t>78337</t>
+          <t>78878</t>
         </is>
       </c>
       <c r="M37" s="2" t="inlineStr">
         <is>
-          <t>106384</t>
+          <t>106461</t>
         </is>
       </c>
       <c r="N37" s="2" t="inlineStr">
@@ -4543,12 +4543,12 @@
       </c>
       <c r="O37" s="2" t="inlineStr">
         <is>
-          <t>11,2%</t>
+          <t>11,28%</t>
         </is>
       </c>
       <c r="P37" s="2" t="inlineStr">
         <is>
-          <t>15,21%</t>
+          <t>15,22%</t>
         </is>
       </c>
       <c r="Q37" s="2" t="inlineStr">
@@ -4563,12 +4563,12 @@
       </c>
       <c r="S37" s="2" t="inlineStr">
         <is>
-          <t>150722</t>
+          <t>151377</t>
         </is>
       </c>
       <c r="T37" s="2" t="inlineStr">
         <is>
-          <t>189952</t>
+          <t>190237</t>
         </is>
       </c>
       <c r="U37" s="2" t="inlineStr">
@@ -4578,12 +4578,12 @@
       </c>
       <c r="V37" s="2" t="inlineStr">
         <is>
-          <t>11,08%</t>
+          <t>11,13%</t>
         </is>
       </c>
       <c r="W37" s="2" t="inlineStr">
         <is>
-          <t>13,96%</t>
+          <t>13,98%</t>
         </is>
       </c>
     </row>
@@ -4606,12 +4606,12 @@
       </c>
       <c r="E38" s="2" t="inlineStr">
         <is>
-          <t>401969</t>
+          <t>403199</t>
         </is>
       </c>
       <c r="F38" s="2" t="inlineStr">
         <is>
-          <t>442491</t>
+          <t>440745</t>
         </is>
       </c>
       <c r="G38" s="2" t="inlineStr">
@@ -4621,12 +4621,12 @@
       </c>
       <c r="H38" s="2" t="inlineStr">
         <is>
-          <t>60,81%</t>
+          <t>61,0%</t>
         </is>
       </c>
       <c r="I38" s="2" t="inlineStr">
         <is>
-          <t>66,94%</t>
+          <t>66,68%</t>
         </is>
       </c>
       <c r="J38" s="2" t="inlineStr">
@@ -4641,12 +4641,12 @@
       </c>
       <c r="L38" s="2" t="inlineStr">
         <is>
-          <t>410571</t>
+          <t>411008</t>
         </is>
       </c>
       <c r="M38" s="2" t="inlineStr">
         <is>
-          <t>451712</t>
+          <t>452874</t>
         </is>
       </c>
       <c r="N38" s="2" t="inlineStr">
@@ -4656,12 +4656,12 @@
       </c>
       <c r="O38" s="2" t="inlineStr">
         <is>
-          <t>58,71%</t>
+          <t>58,77%</t>
         </is>
       </c>
       <c r="P38" s="2" t="inlineStr">
         <is>
-          <t>64,6%</t>
+          <t>64,76%</t>
         </is>
       </c>
       <c r="Q38" s="2" t="inlineStr">
@@ -4676,12 +4676,12 @@
       </c>
       <c r="S38" s="2" t="inlineStr">
         <is>
-          <t>826628</t>
+          <t>824815</t>
         </is>
       </c>
       <c r="T38" s="2" t="inlineStr">
         <is>
-          <t>884332</t>
+          <t>881227</t>
         </is>
       </c>
       <c r="U38" s="2" t="inlineStr">
@@ -4691,12 +4691,12 @@
       </c>
       <c r="V38" s="2" t="inlineStr">
         <is>
-          <t>60,77%</t>
+          <t>60,64%</t>
         </is>
       </c>
       <c r="W38" s="2" t="inlineStr">
         <is>
-          <t>65,01%</t>
+          <t>64,78%</t>
         </is>
       </c>
     </row>
@@ -5072,12 +5072,12 @@
       </c>
       <c r="E4" s="2" t="inlineStr">
         <is>
-          <t>9442</t>
+          <t>9270</t>
         </is>
       </c>
       <c r="F4" s="2" t="inlineStr">
         <is>
-          <t>19775</t>
+          <t>19118</t>
         </is>
       </c>
       <c r="G4" s="2" t="inlineStr">
@@ -5087,12 +5087,12 @@
       </c>
       <c r="H4" s="2" t="inlineStr">
         <is>
-          <t>16,64%</t>
+          <t>16,34%</t>
         </is>
       </c>
       <c r="I4" s="2" t="inlineStr">
         <is>
-          <t>34,85%</t>
+          <t>33,7%</t>
         </is>
       </c>
       <c r="J4" s="2" t="inlineStr">
@@ -5107,12 +5107,12 @@
       </c>
       <c r="L4" s="2" t="inlineStr">
         <is>
-          <t>14369</t>
+          <t>14588</t>
         </is>
       </c>
       <c r="M4" s="2" t="inlineStr">
         <is>
-          <t>27641</t>
+          <t>27216</t>
         </is>
       </c>
       <c r="N4" s="2" t="inlineStr">
@@ -5122,12 +5122,12 @@
       </c>
       <c r="O4" s="2" t="inlineStr">
         <is>
-          <t>22,91%</t>
+          <t>23,26%</t>
         </is>
       </c>
       <c r="P4" s="2" t="inlineStr">
         <is>
-          <t>44,07%</t>
+          <t>43,39%</t>
         </is>
       </c>
       <c r="Q4" s="2" t="inlineStr">
@@ -5142,12 +5142,12 @@
       </c>
       <c r="S4" s="2" t="inlineStr">
         <is>
-          <t>27037</t>
+          <t>26860</t>
         </is>
       </c>
       <c r="T4" s="2" t="inlineStr">
         <is>
-          <t>42691</t>
+          <t>42584</t>
         </is>
       </c>
       <c r="U4" s="2" t="inlineStr">
@@ -5157,12 +5157,12 @@
       </c>
       <c r="V4" s="2" t="inlineStr">
         <is>
-          <t>22,63%</t>
+          <t>22,48%</t>
         </is>
       </c>
       <c r="W4" s="2" t="inlineStr">
         <is>
-          <t>35,74%</t>
+          <t>35,65%</t>
         </is>
       </c>
     </row>
@@ -5185,12 +5185,12 @@
       </c>
       <c r="E5" s="2" t="inlineStr">
         <is>
-          <t>2372</t>
+          <t>2228</t>
         </is>
       </c>
       <c r="F5" s="2" t="inlineStr">
         <is>
-          <t>9724</t>
+          <t>10015</t>
         </is>
       </c>
       <c r="G5" s="2" t="inlineStr">
@@ -5200,12 +5200,12 @@
       </c>
       <c r="H5" s="2" t="inlineStr">
         <is>
-          <t>4,18%</t>
+          <t>3,93%</t>
         </is>
       </c>
       <c r="I5" s="2" t="inlineStr">
         <is>
-          <t>17,14%</t>
+          <t>17,65%</t>
         </is>
       </c>
       <c r="J5" s="2" t="inlineStr">
@@ -5220,12 +5220,12 @@
       </c>
       <c r="L5" s="2" t="inlineStr">
         <is>
-          <t>1797</t>
+          <t>1277</t>
         </is>
       </c>
       <c r="M5" s="2" t="inlineStr">
         <is>
-          <t>8641</t>
+          <t>8158</t>
         </is>
       </c>
       <c r="N5" s="2" t="inlineStr">
@@ -5235,12 +5235,12 @@
       </c>
       <c r="O5" s="2" t="inlineStr">
         <is>
-          <t>2,86%</t>
+          <t>2,04%</t>
         </is>
       </c>
       <c r="P5" s="2" t="inlineStr">
         <is>
-          <t>13,78%</t>
+          <t>13,01%</t>
         </is>
       </c>
       <c r="Q5" s="2" t="inlineStr">
@@ -5255,12 +5255,12 @@
       </c>
       <c r="S5" s="2" t="inlineStr">
         <is>
-          <t>5036</t>
+          <t>4961</t>
         </is>
       </c>
       <c r="T5" s="2" t="inlineStr">
         <is>
-          <t>15417</t>
+          <t>14110</t>
         </is>
       </c>
       <c r="U5" s="2" t="inlineStr">
@@ -5270,12 +5270,12 @@
       </c>
       <c r="V5" s="2" t="inlineStr">
         <is>
-          <t>4,22%</t>
+          <t>4,15%</t>
         </is>
       </c>
       <c r="W5" s="2" t="inlineStr">
         <is>
-          <t>12,91%</t>
+          <t>11,81%</t>
         </is>
       </c>
     </row>
@@ -5298,12 +5298,12 @@
       </c>
       <c r="E6" s="2" t="inlineStr">
         <is>
-          <t>31671</t>
+          <t>31744</t>
         </is>
       </c>
       <c r="F6" s="2" t="inlineStr">
         <is>
-          <t>43293</t>
+          <t>42905</t>
         </is>
       </c>
       <c r="G6" s="2" t="inlineStr">
@@ -5313,12 +5313,12 @@
       </c>
       <c r="H6" s="2" t="inlineStr">
         <is>
-          <t>55,82%</t>
+          <t>55,95%</t>
         </is>
       </c>
       <c r="I6" s="2" t="inlineStr">
         <is>
-          <t>76,31%</t>
+          <t>75,62%</t>
         </is>
       </c>
       <c r="J6" s="2" t="inlineStr">
@@ -5333,12 +5333,12 @@
       </c>
       <c r="L6" s="2" t="inlineStr">
         <is>
-          <t>31121</t>
+          <t>31465</t>
         </is>
       </c>
       <c r="M6" s="2" t="inlineStr">
         <is>
-          <t>44346</t>
+          <t>44282</t>
         </is>
       </c>
       <c r="N6" s="2" t="inlineStr">
@@ -5348,12 +5348,12 @@
       </c>
       <c r="O6" s="2" t="inlineStr">
         <is>
-          <t>49,62%</t>
+          <t>50,16%</t>
         </is>
       </c>
       <c r="P6" s="2" t="inlineStr">
         <is>
-          <t>70,7%</t>
+          <t>70,6%</t>
         </is>
       </c>
       <c r="Q6" s="2" t="inlineStr">
@@ -5368,12 +5368,12 @@
       </c>
       <c r="S6" s="2" t="inlineStr">
         <is>
-          <t>67283</t>
+          <t>66510</t>
         </is>
       </c>
       <c r="T6" s="2" t="inlineStr">
         <is>
-          <t>84096</t>
+          <t>83655</t>
         </is>
       </c>
       <c r="U6" s="2" t="inlineStr">
@@ -5383,12 +5383,12 @@
       </c>
       <c r="V6" s="2" t="inlineStr">
         <is>
-          <t>56,32%</t>
+          <t>55,68%</t>
         </is>
       </c>
       <c r="W6" s="2" t="inlineStr">
         <is>
-          <t>70,4%</t>
+          <t>70,03%</t>
         </is>
       </c>
     </row>
@@ -5528,12 +5528,12 @@
       </c>
       <c r="E8" s="2" t="inlineStr">
         <is>
-          <t>34066</t>
+          <t>33509</t>
         </is>
       </c>
       <c r="F8" s="2" t="inlineStr">
         <is>
-          <t>50251</t>
+          <t>50308</t>
         </is>
       </c>
       <c r="G8" s="2" t="inlineStr">
@@ -5543,12 +5543,12 @@
       </c>
       <c r="H8" s="2" t="inlineStr">
         <is>
-          <t>32,94%</t>
+          <t>32,4%</t>
         </is>
       </c>
       <c r="I8" s="2" t="inlineStr">
         <is>
-          <t>48,59%</t>
+          <t>48,65%</t>
         </is>
       </c>
       <c r="J8" s="2" t="inlineStr">
@@ -5563,12 +5563,12 @@
       </c>
       <c r="L8" s="2" t="inlineStr">
         <is>
-          <t>31831</t>
+          <t>32504</t>
         </is>
       </c>
       <c r="M8" s="2" t="inlineStr">
         <is>
-          <t>49097</t>
+          <t>48536</t>
         </is>
       </c>
       <c r="N8" s="2" t="inlineStr">
@@ -5578,12 +5578,12 @@
       </c>
       <c r="O8" s="2" t="inlineStr">
         <is>
-          <t>28,81%</t>
+          <t>29,42%</t>
         </is>
       </c>
       <c r="P8" s="2" t="inlineStr">
         <is>
-          <t>44,44%</t>
+          <t>43,93%</t>
         </is>
       </c>
       <c r="Q8" s="2" t="inlineStr">
@@ -5598,12 +5598,12 @@
       </c>
       <c r="S8" s="2" t="inlineStr">
         <is>
-          <t>71583</t>
+          <t>70864</t>
         </is>
       </c>
       <c r="T8" s="2" t="inlineStr">
         <is>
-          <t>93954</t>
+          <t>94325</t>
         </is>
       </c>
       <c r="U8" s="2" t="inlineStr">
@@ -5613,12 +5613,12 @@
       </c>
       <c r="V8" s="2" t="inlineStr">
         <is>
-          <t>33,47%</t>
+          <t>33,13%</t>
         </is>
       </c>
       <c r="W8" s="2" t="inlineStr">
         <is>
-          <t>43,93%</t>
+          <t>44,1%</t>
         </is>
       </c>
     </row>
@@ -5641,12 +5641,12 @@
       </c>
       <c r="E9" s="2" t="inlineStr">
         <is>
-          <t>7977</t>
+          <t>7995</t>
         </is>
       </c>
       <c r="F9" s="2" t="inlineStr">
         <is>
-          <t>18852</t>
+          <t>19141</t>
         </is>
       </c>
       <c r="G9" s="2" t="inlineStr">
@@ -5656,12 +5656,12 @@
       </c>
       <c r="H9" s="2" t="inlineStr">
         <is>
-          <t>7,71%</t>
+          <t>7,73%</t>
         </is>
       </c>
       <c r="I9" s="2" t="inlineStr">
         <is>
-          <t>18,23%</t>
+          <t>18,51%</t>
         </is>
       </c>
       <c r="J9" s="2" t="inlineStr">
@@ -5676,12 +5676,12 @@
       </c>
       <c r="L9" s="2" t="inlineStr">
         <is>
-          <t>13398</t>
+          <t>13115</t>
         </is>
       </c>
       <c r="M9" s="2" t="inlineStr">
         <is>
-          <t>25716</t>
+          <t>25130</t>
         </is>
       </c>
       <c r="N9" s="2" t="inlineStr">
@@ -5691,12 +5691,12 @@
       </c>
       <c r="O9" s="2" t="inlineStr">
         <is>
-          <t>12,13%</t>
+          <t>11,87%</t>
         </is>
       </c>
       <c r="P9" s="2" t="inlineStr">
         <is>
-          <t>23,28%</t>
+          <t>22,75%</t>
         </is>
       </c>
       <c r="Q9" s="2" t="inlineStr">
@@ -5711,12 +5711,12 @@
       </c>
       <c r="S9" s="2" t="inlineStr">
         <is>
-          <t>24188</t>
+          <t>24355</t>
         </is>
       </c>
       <c r="T9" s="2" t="inlineStr">
         <is>
-          <t>40288</t>
+          <t>41343</t>
         </is>
       </c>
       <c r="U9" s="2" t="inlineStr">
@@ -5726,12 +5726,12 @@
       </c>
       <c r="V9" s="2" t="inlineStr">
         <is>
-          <t>11,31%</t>
+          <t>11,39%</t>
         </is>
       </c>
       <c r="W9" s="2" t="inlineStr">
         <is>
-          <t>18,84%</t>
+          <t>19,33%</t>
         </is>
       </c>
     </row>
@@ -5754,12 +5754,12 @@
       </c>
       <c r="E10" s="2" t="inlineStr">
         <is>
-          <t>40587</t>
+          <t>40264</t>
         </is>
       </c>
       <c r="F10" s="2" t="inlineStr">
         <is>
-          <t>57389</t>
+          <t>56779</t>
         </is>
       </c>
       <c r="G10" s="2" t="inlineStr">
@@ -5769,12 +5769,12 @@
       </c>
       <c r="H10" s="2" t="inlineStr">
         <is>
-          <t>39,25%</t>
+          <t>38,94%</t>
         </is>
       </c>
       <c r="I10" s="2" t="inlineStr">
         <is>
-          <t>55,5%</t>
+          <t>54,91%</t>
         </is>
       </c>
       <c r="J10" s="2" t="inlineStr">
@@ -5789,12 +5789,12 @@
       </c>
       <c r="L10" s="2" t="inlineStr">
         <is>
-          <t>43240</t>
+          <t>43169</t>
         </is>
       </c>
       <c r="M10" s="2" t="inlineStr">
         <is>
-          <t>60521</t>
+          <t>60012</t>
         </is>
       </c>
       <c r="N10" s="2" t="inlineStr">
@@ -5804,12 +5804,12 @@
       </c>
       <c r="O10" s="2" t="inlineStr">
         <is>
-          <t>39,14%</t>
+          <t>39,07%</t>
         </is>
       </c>
       <c r="P10" s="2" t="inlineStr">
         <is>
-          <t>54,78%</t>
+          <t>54,32%</t>
         </is>
       </c>
       <c r="Q10" s="2" t="inlineStr">
@@ -5824,12 +5824,12 @@
       </c>
       <c r="S10" s="2" t="inlineStr">
         <is>
-          <t>88315</t>
+          <t>88340</t>
         </is>
       </c>
       <c r="T10" s="2" t="inlineStr">
         <is>
-          <t>112466</t>
+          <t>112341</t>
         </is>
       </c>
       <c r="U10" s="2" t="inlineStr">
@@ -5839,12 +5839,12 @@
       </c>
       <c r="V10" s="2" t="inlineStr">
         <is>
-          <t>41,29%</t>
+          <t>41,3%</t>
         </is>
       </c>
       <c r="W10" s="2" t="inlineStr">
         <is>
-          <t>52,58%</t>
+          <t>52,52%</t>
         </is>
       </c>
     </row>
@@ -5984,12 +5984,12 @@
       </c>
       <c r="E12" s="2" t="inlineStr">
         <is>
-          <t>10231</t>
+          <t>10115</t>
         </is>
       </c>
       <c r="F12" s="2" t="inlineStr">
         <is>
-          <t>21836</t>
+          <t>21983</t>
         </is>
       </c>
       <c r="G12" s="2" t="inlineStr">
@@ -5999,12 +5999,12 @@
       </c>
       <c r="H12" s="2" t="inlineStr">
         <is>
-          <t>15,16%</t>
+          <t>14,99%</t>
         </is>
       </c>
       <c r="I12" s="2" t="inlineStr">
         <is>
-          <t>32,35%</t>
+          <t>32,57%</t>
         </is>
       </c>
       <c r="J12" s="2" t="inlineStr">
@@ -6019,12 +6019,12 @@
       </c>
       <c r="L12" s="2" t="inlineStr">
         <is>
-          <t>15838</t>
+          <t>15588</t>
         </is>
       </c>
       <c r="M12" s="2" t="inlineStr">
         <is>
-          <t>28537</t>
+          <t>28862</t>
         </is>
       </c>
       <c r="N12" s="2" t="inlineStr">
@@ -6034,12 +6034,12 @@
       </c>
       <c r="O12" s="2" t="inlineStr">
         <is>
-          <t>22,45%</t>
+          <t>22,1%</t>
         </is>
       </c>
       <c r="P12" s="2" t="inlineStr">
         <is>
-          <t>40,46%</t>
+          <t>40,92%</t>
         </is>
       </c>
       <c r="Q12" s="2" t="inlineStr">
@@ -6054,12 +6054,12 @@
       </c>
       <c r="S12" s="2" t="inlineStr">
         <is>
-          <t>29838</t>
+          <t>29573</t>
         </is>
       </c>
       <c r="T12" s="2" t="inlineStr">
         <is>
-          <t>46731</t>
+          <t>46773</t>
         </is>
       </c>
       <c r="U12" s="2" t="inlineStr">
@@ -6069,12 +6069,12 @@
       </c>
       <c r="V12" s="2" t="inlineStr">
         <is>
-          <t>21,62%</t>
+          <t>21,42%</t>
         </is>
       </c>
       <c r="W12" s="2" t="inlineStr">
         <is>
-          <t>33,85%</t>
+          <t>33,88%</t>
         </is>
       </c>
     </row>
@@ -6097,12 +6097,12 @@
       </c>
       <c r="E13" s="2" t="inlineStr">
         <is>
-          <t>2331</t>
+          <t>2708</t>
         </is>
       </c>
       <c r="F13" s="2" t="inlineStr">
         <is>
-          <t>10723</t>
+          <t>11020</t>
         </is>
       </c>
       <c r="G13" s="2" t="inlineStr">
@@ -6112,12 +6112,12 @@
       </c>
       <c r="H13" s="2" t="inlineStr">
         <is>
-          <t>3,45%</t>
+          <t>4,01%</t>
         </is>
       </c>
       <c r="I13" s="2" t="inlineStr">
         <is>
-          <t>15,89%</t>
+          <t>16,33%</t>
         </is>
       </c>
       <c r="J13" s="2" t="inlineStr">
@@ -6132,12 +6132,12 @@
       </c>
       <c r="L13" s="2" t="inlineStr">
         <is>
-          <t>3459</t>
+          <t>3412</t>
         </is>
       </c>
       <c r="M13" s="2" t="inlineStr">
         <is>
-          <t>12097</t>
+          <t>11624</t>
         </is>
       </c>
       <c r="N13" s="2" t="inlineStr">
@@ -6147,12 +6147,12 @@
       </c>
       <c r="O13" s="2" t="inlineStr">
         <is>
-          <t>4,9%</t>
+          <t>4,84%</t>
         </is>
       </c>
       <c r="P13" s="2" t="inlineStr">
         <is>
-          <t>17,15%</t>
+          <t>16,48%</t>
         </is>
       </c>
       <c r="Q13" s="2" t="inlineStr">
@@ -6167,12 +6167,12 @@
       </c>
       <c r="S13" s="2" t="inlineStr">
         <is>
-          <t>7544</t>
+          <t>7757</t>
         </is>
       </c>
       <c r="T13" s="2" t="inlineStr">
         <is>
-          <t>19217</t>
+          <t>19363</t>
         </is>
       </c>
       <c r="U13" s="2" t="inlineStr">
@@ -6182,12 +6182,12 @@
       </c>
       <c r="V13" s="2" t="inlineStr">
         <is>
-          <t>5,47%</t>
+          <t>5,62%</t>
         </is>
       </c>
       <c r="W13" s="2" t="inlineStr">
         <is>
-          <t>13,92%</t>
+          <t>14,03%</t>
         </is>
       </c>
     </row>
@@ -6210,12 +6210,12 @@
       </c>
       <c r="E14" s="2" t="inlineStr">
         <is>
-          <t>39636</t>
+          <t>39635</t>
         </is>
       </c>
       <c r="F14" s="2" t="inlineStr">
         <is>
-          <t>52044</t>
+          <t>52297</t>
         </is>
       </c>
       <c r="G14" s="2" t="inlineStr">
@@ -6230,7 +6230,7 @@
       </c>
       <c r="I14" s="2" t="inlineStr">
         <is>
-          <t>77,1%</t>
+          <t>77,48%</t>
         </is>
       </c>
       <c r="J14" s="2" t="inlineStr">
@@ -6245,12 +6245,12 @@
       </c>
       <c r="L14" s="2" t="inlineStr">
         <is>
-          <t>34622</t>
+          <t>34734</t>
         </is>
       </c>
       <c r="M14" s="2" t="inlineStr">
         <is>
-          <t>48335</t>
+          <t>48176</t>
         </is>
       </c>
       <c r="N14" s="2" t="inlineStr">
@@ -6260,12 +6260,12 @@
       </c>
       <c r="O14" s="2" t="inlineStr">
         <is>
-          <t>49,08%</t>
+          <t>49,24%</t>
         </is>
       </c>
       <c r="P14" s="2" t="inlineStr">
         <is>
-          <t>68,52%</t>
+          <t>68,3%</t>
         </is>
       </c>
       <c r="Q14" s="2" t="inlineStr">
@@ -6280,12 +6280,12 @@
       </c>
       <c r="S14" s="2" t="inlineStr">
         <is>
-          <t>78168</t>
+          <t>78378</t>
         </is>
       </c>
       <c r="T14" s="2" t="inlineStr">
         <is>
-          <t>96274</t>
+          <t>96532</t>
         </is>
       </c>
       <c r="U14" s="2" t="inlineStr">
@@ -6295,12 +6295,12 @@
       </c>
       <c r="V14" s="2" t="inlineStr">
         <is>
-          <t>56,63%</t>
+          <t>56,78%</t>
         </is>
       </c>
       <c r="W14" s="2" t="inlineStr">
         <is>
-          <t>69,74%</t>
+          <t>69,93%</t>
         </is>
       </c>
     </row>
@@ -6440,7 +6440,7 @@
       </c>
       <c r="E16" s="2" t="inlineStr">
         <is>
-          <t>14568</t>
+          <t>14935</t>
         </is>
       </c>
       <c r="F16" s="2" t="inlineStr">
@@ -6455,7 +6455,7 @@
       </c>
       <c r="H16" s="2" t="inlineStr">
         <is>
-          <t>18,89%</t>
+          <t>19,37%</t>
         </is>
       </c>
       <c r="I16" s="2" t="inlineStr">
@@ -6475,12 +6475,12 @@
       </c>
       <c r="L16" s="2" t="inlineStr">
         <is>
-          <t>14158</t>
+          <t>14301</t>
         </is>
       </c>
       <c r="M16" s="2" t="inlineStr">
         <is>
-          <t>27582</t>
+          <t>27780</t>
         </is>
       </c>
       <c r="N16" s="2" t="inlineStr">
@@ -6490,12 +6490,12 @@
       </c>
       <c r="O16" s="2" t="inlineStr">
         <is>
-          <t>17,57%</t>
+          <t>17,75%</t>
         </is>
       </c>
       <c r="P16" s="2" t="inlineStr">
         <is>
-          <t>34,24%</t>
+          <t>34,48%</t>
         </is>
       </c>
       <c r="Q16" s="2" t="inlineStr">
@@ -6510,12 +6510,12 @@
       </c>
       <c r="S16" s="2" t="inlineStr">
         <is>
-          <t>31090</t>
+          <t>31511</t>
         </is>
       </c>
       <c r="T16" s="2" t="inlineStr">
         <is>
-          <t>49525</t>
+          <t>49393</t>
         </is>
       </c>
       <c r="U16" s="2" t="inlineStr">
@@ -6525,12 +6525,12 @@
       </c>
       <c r="V16" s="2" t="inlineStr">
         <is>
-          <t>19,72%</t>
+          <t>19,99%</t>
         </is>
       </c>
       <c r="W16" s="2" t="inlineStr">
         <is>
-          <t>31,41%</t>
+          <t>31,33%</t>
         </is>
       </c>
     </row>
@@ -6553,12 +6553,12 @@
       </c>
       <c r="E17" s="2" t="inlineStr">
         <is>
-          <t>3155</t>
+          <t>3066</t>
         </is>
       </c>
       <c r="F17" s="2" t="inlineStr">
         <is>
-          <t>10709</t>
+          <t>10591</t>
         </is>
       </c>
       <c r="G17" s="2" t="inlineStr">
@@ -6568,12 +6568,12 @@
       </c>
       <c r="H17" s="2" t="inlineStr">
         <is>
-          <t>4,09%</t>
+          <t>3,98%</t>
         </is>
       </c>
       <c r="I17" s="2" t="inlineStr">
         <is>
-          <t>13,89%</t>
+          <t>13,73%</t>
         </is>
       </c>
       <c r="J17" s="2" t="inlineStr">
@@ -6588,12 +6588,12 @@
       </c>
       <c r="L17" s="2" t="inlineStr">
         <is>
-          <t>2844</t>
+          <t>2898</t>
         </is>
       </c>
       <c r="M17" s="2" t="inlineStr">
         <is>
-          <t>11686</t>
+          <t>11239</t>
         </is>
       </c>
       <c r="N17" s="2" t="inlineStr">
@@ -6603,12 +6603,12 @@
       </c>
       <c r="O17" s="2" t="inlineStr">
         <is>
-          <t>3,53%</t>
+          <t>3,6%</t>
         </is>
       </c>
       <c r="P17" s="2" t="inlineStr">
         <is>
-          <t>14,51%</t>
+          <t>13,95%</t>
         </is>
       </c>
       <c r="Q17" s="2" t="inlineStr">
@@ -6623,12 +6623,12 @@
       </c>
       <c r="S17" s="2" t="inlineStr">
         <is>
-          <t>7359</t>
+          <t>8031</t>
         </is>
       </c>
       <c r="T17" s="2" t="inlineStr">
         <is>
-          <t>18789</t>
+          <t>19614</t>
         </is>
       </c>
       <c r="U17" s="2" t="inlineStr">
@@ -6638,12 +6638,12 @@
       </c>
       <c r="V17" s="2" t="inlineStr">
         <is>
-          <t>4,67%</t>
+          <t>5,09%</t>
         </is>
       </c>
       <c r="W17" s="2" t="inlineStr">
         <is>
-          <t>11,92%</t>
+          <t>12,44%</t>
         </is>
       </c>
     </row>
@@ -6666,12 +6666,12 @@
       </c>
       <c r="E18" s="2" t="inlineStr">
         <is>
-          <t>44062</t>
+          <t>43098</t>
         </is>
       </c>
       <c r="F18" s="2" t="inlineStr">
         <is>
-          <t>57339</t>
+          <t>57226</t>
         </is>
       </c>
       <c r="G18" s="2" t="inlineStr">
@@ -6681,12 +6681,12 @@
       </c>
       <c r="H18" s="2" t="inlineStr">
         <is>
-          <t>57,14%</t>
+          <t>55,89%</t>
         </is>
       </c>
       <c r="I18" s="2" t="inlineStr">
         <is>
-          <t>74,36%</t>
+          <t>74,21%</t>
         </is>
       </c>
       <c r="J18" s="2" t="inlineStr">
@@ -6701,12 +6701,12 @@
       </c>
       <c r="L18" s="2" t="inlineStr">
         <is>
-          <t>46629</t>
+          <t>46470</t>
         </is>
       </c>
       <c r="M18" s="2" t="inlineStr">
         <is>
-          <t>61074</t>
+          <t>60808</t>
         </is>
       </c>
       <c r="N18" s="2" t="inlineStr">
@@ -6716,12 +6716,12 @@
       </c>
       <c r="O18" s="2" t="inlineStr">
         <is>
-          <t>57,88%</t>
+          <t>57,68%</t>
         </is>
       </c>
       <c r="P18" s="2" t="inlineStr">
         <is>
-          <t>75,81%</t>
+          <t>75,48%</t>
         </is>
       </c>
       <c r="Q18" s="2" t="inlineStr">
@@ -6736,12 +6736,12 @@
       </c>
       <c r="S18" s="2" t="inlineStr">
         <is>
-          <t>95447</t>
+          <t>95021</t>
         </is>
       </c>
       <c r="T18" s="2" t="inlineStr">
         <is>
-          <t>114726</t>
+          <t>114455</t>
         </is>
       </c>
       <c r="U18" s="2" t="inlineStr">
@@ -6751,12 +6751,12 @@
       </c>
       <c r="V18" s="2" t="inlineStr">
         <is>
-          <t>60,53%</t>
+          <t>60,26%</t>
         </is>
       </c>
       <c r="W18" s="2" t="inlineStr">
         <is>
-          <t>72,76%</t>
+          <t>72,59%</t>
         </is>
       </c>
     </row>
@@ -6896,12 +6896,12 @@
       </c>
       <c r="E20" s="2" t="inlineStr">
         <is>
-          <t>14778</t>
+          <t>15023</t>
         </is>
       </c>
       <c r="F20" s="2" t="inlineStr">
         <is>
-          <t>26316</t>
+          <t>26077</t>
         </is>
       </c>
       <c r="G20" s="2" t="inlineStr">
@@ -6911,12 +6911,12 @@
       </c>
       <c r="H20" s="2" t="inlineStr">
         <is>
-          <t>34,2%</t>
+          <t>34,77%</t>
         </is>
       </c>
       <c r="I20" s="2" t="inlineStr">
         <is>
-          <t>60,9%</t>
+          <t>60,35%</t>
         </is>
       </c>
       <c r="J20" s="2" t="inlineStr">
@@ -6931,12 +6931,12 @@
       </c>
       <c r="L20" s="2" t="inlineStr">
         <is>
-          <t>19575</t>
+          <t>20635</t>
         </is>
       </c>
       <c r="M20" s="2" t="inlineStr">
         <is>
-          <t>31147</t>
+          <t>31772</t>
         </is>
       </c>
       <c r="N20" s="2" t="inlineStr">
@@ -6946,12 +6946,12 @@
       </c>
       <c r="O20" s="2" t="inlineStr">
         <is>
-          <t>44,51%</t>
+          <t>46,92%</t>
         </is>
       </c>
       <c r="P20" s="2" t="inlineStr">
         <is>
-          <t>70,83%</t>
+          <t>72,25%</t>
         </is>
       </c>
       <c r="Q20" s="2" t="inlineStr">
@@ -6966,12 +6966,12 @@
       </c>
       <c r="S20" s="2" t="inlineStr">
         <is>
-          <t>37670</t>
+          <t>38018</t>
         </is>
       </c>
       <c r="T20" s="2" t="inlineStr">
         <is>
-          <t>53761</t>
+          <t>54210</t>
         </is>
       </c>
       <c r="U20" s="2" t="inlineStr">
@@ -6981,12 +6981,12 @@
       </c>
       <c r="V20" s="2" t="inlineStr">
         <is>
-          <t>43,21%</t>
+          <t>43,6%</t>
         </is>
       </c>
       <c r="W20" s="2" t="inlineStr">
         <is>
-          <t>61,66%</t>
+          <t>62,18%</t>
         </is>
       </c>
     </row>
@@ -7009,12 +7009,12 @@
       </c>
       <c r="E21" s="2" t="inlineStr">
         <is>
-          <t>2224</t>
+          <t>2231</t>
         </is>
       </c>
       <c r="F21" s="2" t="inlineStr">
         <is>
-          <t>9820</t>
+          <t>10117</t>
         </is>
       </c>
       <c r="G21" s="2" t="inlineStr">
@@ -7024,12 +7024,12 @@
       </c>
       <c r="H21" s="2" t="inlineStr">
         <is>
-          <t>5,15%</t>
+          <t>5,16%</t>
         </is>
       </c>
       <c r="I21" s="2" t="inlineStr">
         <is>
-          <t>22,73%</t>
+          <t>23,41%</t>
         </is>
       </c>
       <c r="J21" s="2" t="inlineStr">
@@ -7044,12 +7044,12 @@
       </c>
       <c r="L21" s="2" t="inlineStr">
         <is>
-          <t>657</t>
+          <t>643</t>
         </is>
       </c>
       <c r="M21" s="2" t="inlineStr">
         <is>
-          <t>7037</t>
+          <t>6566</t>
         </is>
       </c>
       <c r="N21" s="2" t="inlineStr">
@@ -7059,12 +7059,12 @@
       </c>
       <c r="O21" s="2" t="inlineStr">
         <is>
-          <t>1,49%</t>
+          <t>1,46%</t>
         </is>
       </c>
       <c r="P21" s="2" t="inlineStr">
         <is>
-          <t>16,0%</t>
+          <t>14,93%</t>
         </is>
       </c>
       <c r="Q21" s="2" t="inlineStr">
@@ -7079,12 +7079,12 @@
       </c>
       <c r="S21" s="2" t="inlineStr">
         <is>
-          <t>3922</t>
+          <t>4079</t>
         </is>
       </c>
       <c r="T21" s="2" t="inlineStr">
         <is>
-          <t>13381</t>
+          <t>13321</t>
         </is>
       </c>
       <c r="U21" s="2" t="inlineStr">
@@ -7094,12 +7094,12 @@
       </c>
       <c r="V21" s="2" t="inlineStr">
         <is>
-          <t>4,5%</t>
+          <t>4,68%</t>
         </is>
       </c>
       <c r="W21" s="2" t="inlineStr">
         <is>
-          <t>15,35%</t>
+          <t>15,28%</t>
         </is>
       </c>
     </row>
@@ -7122,12 +7122,12 @@
       </c>
       <c r="E22" s="2" t="inlineStr">
         <is>
-          <t>11943</t>
+          <t>12047</t>
         </is>
       </c>
       <c r="F22" s="2" t="inlineStr">
         <is>
-          <t>23369</t>
+          <t>23287</t>
         </is>
       </c>
       <c r="G22" s="2" t="inlineStr">
@@ -7137,12 +7137,12 @@
       </c>
       <c r="H22" s="2" t="inlineStr">
         <is>
-          <t>27,64%</t>
+          <t>27,88%</t>
         </is>
       </c>
       <c r="I22" s="2" t="inlineStr">
         <is>
-          <t>54,08%</t>
+          <t>53,89%</t>
         </is>
       </c>
       <c r="J22" s="2" t="inlineStr">
@@ -7157,12 +7157,12 @@
       </c>
       <c r="L22" s="2" t="inlineStr">
         <is>
-          <t>10613</t>
+          <t>10462</t>
         </is>
       </c>
       <c r="M22" s="2" t="inlineStr">
         <is>
-          <t>21469</t>
+          <t>20874</t>
         </is>
       </c>
       <c r="N22" s="2" t="inlineStr">
@@ -7172,12 +7172,12 @@
       </c>
       <c r="O22" s="2" t="inlineStr">
         <is>
-          <t>24,13%</t>
+          <t>23,79%</t>
         </is>
       </c>
       <c r="P22" s="2" t="inlineStr">
         <is>
-          <t>48,82%</t>
+          <t>47,47%</t>
         </is>
       </c>
       <c r="Q22" s="2" t="inlineStr">
@@ -7192,12 +7192,12 @@
       </c>
       <c r="S22" s="2" t="inlineStr">
         <is>
-          <t>26314</t>
+          <t>25879</t>
         </is>
       </c>
       <c r="T22" s="2" t="inlineStr">
         <is>
-          <t>41281</t>
+          <t>41148</t>
         </is>
       </c>
       <c r="U22" s="2" t="inlineStr">
@@ -7207,12 +7207,12 @@
       </c>
       <c r="V22" s="2" t="inlineStr">
         <is>
-          <t>30,18%</t>
+          <t>29,68%</t>
         </is>
       </c>
       <c r="W22" s="2" t="inlineStr">
         <is>
-          <t>47,35%</t>
+          <t>47,19%</t>
         </is>
       </c>
     </row>
@@ -7352,12 +7352,12 @@
       </c>
       <c r="E24" s="2" t="inlineStr">
         <is>
-          <t>3366</t>
+          <t>3378</t>
         </is>
       </c>
       <c r="F24" s="2" t="inlineStr">
         <is>
-          <t>11411</t>
+          <t>11855</t>
         </is>
       </c>
       <c r="G24" s="2" t="inlineStr">
@@ -7367,12 +7367,12 @@
       </c>
       <c r="H24" s="2" t="inlineStr">
         <is>
-          <t>6,09%</t>
+          <t>6,11%</t>
         </is>
       </c>
       <c r="I24" s="2" t="inlineStr">
         <is>
-          <t>20,65%</t>
+          <t>21,45%</t>
         </is>
       </c>
       <c r="J24" s="2" t="inlineStr">
@@ -7387,12 +7387,12 @@
       </c>
       <c r="L24" s="2" t="inlineStr">
         <is>
-          <t>6774</t>
+          <t>6846</t>
         </is>
       </c>
       <c r="M24" s="2" t="inlineStr">
         <is>
-          <t>17224</t>
+          <t>16547</t>
         </is>
       </c>
       <c r="N24" s="2" t="inlineStr">
@@ -7402,12 +7402,12 @@
       </c>
       <c r="O24" s="2" t="inlineStr">
         <is>
-          <t>11,24%</t>
+          <t>11,36%</t>
         </is>
       </c>
       <c r="P24" s="2" t="inlineStr">
         <is>
-          <t>28,59%</t>
+          <t>27,47%</t>
         </is>
       </c>
       <c r="Q24" s="2" t="inlineStr">
@@ -7422,12 +7422,12 @@
       </c>
       <c r="S24" s="2" t="inlineStr">
         <is>
-          <t>11960</t>
+          <t>12329</t>
         </is>
       </c>
       <c r="T24" s="2" t="inlineStr">
         <is>
-          <t>25392</t>
+          <t>24995</t>
         </is>
       </c>
       <c r="U24" s="2" t="inlineStr">
@@ -7437,12 +7437,12 @@
       </c>
       <c r="V24" s="2" t="inlineStr">
         <is>
-          <t>10,35%</t>
+          <t>10,67%</t>
         </is>
       </c>
       <c r="W24" s="2" t="inlineStr">
         <is>
-          <t>21,98%</t>
+          <t>21,64%</t>
         </is>
       </c>
     </row>
@@ -7465,12 +7465,12 @@
       </c>
       <c r="E25" s="2" t="inlineStr">
         <is>
-          <t>5968</t>
+          <t>6036</t>
         </is>
       </c>
       <c r="F25" s="2" t="inlineStr">
         <is>
-          <t>15226</t>
+          <t>15595</t>
         </is>
       </c>
       <c r="G25" s="2" t="inlineStr">
@@ -7480,12 +7480,12 @@
       </c>
       <c r="H25" s="2" t="inlineStr">
         <is>
-          <t>10,8%</t>
+          <t>10,92%</t>
         </is>
       </c>
       <c r="I25" s="2" t="inlineStr">
         <is>
-          <t>27,55%</t>
+          <t>28,21%</t>
         </is>
       </c>
       <c r="J25" s="2" t="inlineStr">
@@ -7500,12 +7500,12 @@
       </c>
       <c r="L25" s="2" t="inlineStr">
         <is>
-          <t>2609</t>
+          <t>2397</t>
         </is>
       </c>
       <c r="M25" s="2" t="inlineStr">
         <is>
-          <t>10173</t>
+          <t>10348</t>
         </is>
       </c>
       <c r="N25" s="2" t="inlineStr">
@@ -7515,12 +7515,12 @@
       </c>
       <c r="O25" s="2" t="inlineStr">
         <is>
-          <t>4,33%</t>
+          <t>3,98%</t>
         </is>
       </c>
       <c r="P25" s="2" t="inlineStr">
         <is>
-          <t>16,89%</t>
+          <t>17,18%</t>
         </is>
       </c>
       <c r="Q25" s="2" t="inlineStr">
@@ -7535,12 +7535,12 @@
       </c>
       <c r="S25" s="2" t="inlineStr">
         <is>
-          <t>10131</t>
+          <t>9912</t>
         </is>
       </c>
       <c r="T25" s="2" t="inlineStr">
         <is>
-          <t>21987</t>
+          <t>22392</t>
         </is>
       </c>
       <c r="U25" s="2" t="inlineStr">
@@ -7550,12 +7550,12 @@
       </c>
       <c r="V25" s="2" t="inlineStr">
         <is>
-          <t>8,77%</t>
+          <t>8,58%</t>
         </is>
       </c>
       <c r="W25" s="2" t="inlineStr">
         <is>
-          <t>19,03%</t>
+          <t>19,38%</t>
         </is>
       </c>
     </row>
@@ -7578,12 +7578,12 @@
       </c>
       <c r="E26" s="2" t="inlineStr">
         <is>
-          <t>32948</t>
+          <t>32139</t>
         </is>
       </c>
       <c r="F26" s="2" t="inlineStr">
         <is>
-          <t>44295</t>
+          <t>43637</t>
         </is>
       </c>
       <c r="G26" s="2" t="inlineStr">
@@ -7593,12 +7593,12 @@
       </c>
       <c r="H26" s="2" t="inlineStr">
         <is>
-          <t>59,61%</t>
+          <t>58,15%</t>
         </is>
       </c>
       <c r="I26" s="2" t="inlineStr">
         <is>
-          <t>80,14%</t>
+          <t>78,95%</t>
         </is>
       </c>
       <c r="J26" s="2" t="inlineStr">
@@ -7613,12 +7613,12 @@
       </c>
       <c r="L26" s="2" t="inlineStr">
         <is>
-          <t>37587</t>
+          <t>37850</t>
         </is>
       </c>
       <c r="M26" s="2" t="inlineStr">
         <is>
-          <t>49312</t>
+          <t>49055</t>
         </is>
       </c>
       <c r="N26" s="2" t="inlineStr">
@@ -7628,12 +7628,12 @@
       </c>
       <c r="O26" s="2" t="inlineStr">
         <is>
-          <t>62,39%</t>
+          <t>62,83%</t>
         </is>
       </c>
       <c r="P26" s="2" t="inlineStr">
         <is>
-          <t>81,85%</t>
+          <t>81,43%</t>
         </is>
       </c>
       <c r="Q26" s="2" t="inlineStr">
@@ -7648,12 +7648,12 @@
       </c>
       <c r="S26" s="2" t="inlineStr">
         <is>
-          <t>73538</t>
+          <t>74314</t>
         </is>
       </c>
       <c r="T26" s="2" t="inlineStr">
         <is>
-          <t>89914</t>
+          <t>90241</t>
         </is>
       </c>
       <c r="U26" s="2" t="inlineStr">
@@ -7663,12 +7663,12 @@
       </c>
       <c r="V26" s="2" t="inlineStr">
         <is>
-          <t>63,66%</t>
+          <t>64,33%</t>
         </is>
       </c>
       <c r="W26" s="2" t="inlineStr">
         <is>
-          <t>77,84%</t>
+          <t>78,12%</t>
         </is>
       </c>
     </row>
@@ -7808,12 +7808,12 @@
       </c>
       <c r="E28" s="2" t="inlineStr">
         <is>
-          <t>25570</t>
+          <t>25240</t>
         </is>
       </c>
       <c r="F28" s="2" t="inlineStr">
         <is>
-          <t>42942</t>
+          <t>41692</t>
         </is>
       </c>
       <c r="G28" s="2" t="inlineStr">
@@ -7823,12 +7823,12 @@
       </c>
       <c r="H28" s="2" t="inlineStr">
         <is>
-          <t>18,67%</t>
+          <t>18,43%</t>
         </is>
       </c>
       <c r="I28" s="2" t="inlineStr">
         <is>
-          <t>31,36%</t>
+          <t>30,44%</t>
         </is>
       </c>
       <c r="J28" s="2" t="inlineStr">
@@ -7843,12 +7843,12 @@
       </c>
       <c r="L28" s="2" t="inlineStr">
         <is>
-          <t>21247</t>
+          <t>21267</t>
         </is>
       </c>
       <c r="M28" s="2" t="inlineStr">
         <is>
-          <t>37150</t>
+          <t>36689</t>
         </is>
       </c>
       <c r="N28" s="2" t="inlineStr">
@@ -7858,12 +7858,12 @@
       </c>
       <c r="O28" s="2" t="inlineStr">
         <is>
-          <t>14,75%</t>
+          <t>14,76%</t>
         </is>
       </c>
       <c r="P28" s="2" t="inlineStr">
         <is>
-          <t>25,78%</t>
+          <t>25,46%</t>
         </is>
       </c>
       <c r="Q28" s="2" t="inlineStr">
@@ -7878,12 +7878,12 @@
       </c>
       <c r="S28" s="2" t="inlineStr">
         <is>
-          <t>50859</t>
+          <t>50810</t>
         </is>
       </c>
       <c r="T28" s="2" t="inlineStr">
         <is>
-          <t>73358</t>
+          <t>74063</t>
         </is>
       </c>
       <c r="U28" s="2" t="inlineStr">
@@ -7893,12 +7893,12 @@
       </c>
       <c r="V28" s="2" t="inlineStr">
         <is>
-          <t>18,1%</t>
+          <t>18,08%</t>
         </is>
       </c>
       <c r="W28" s="2" t="inlineStr">
         <is>
-          <t>26,1%</t>
+          <t>26,35%</t>
         </is>
       </c>
     </row>
@@ -7921,12 +7921,12 @@
       </c>
       <c r="E29" s="2" t="inlineStr">
         <is>
-          <t>10822</t>
+          <t>10721</t>
         </is>
       </c>
       <c r="F29" s="2" t="inlineStr">
         <is>
-          <t>24020</t>
+          <t>22981</t>
         </is>
       </c>
       <c r="G29" s="2" t="inlineStr">
@@ -7936,12 +7936,12 @@
       </c>
       <c r="H29" s="2" t="inlineStr">
         <is>
-          <t>7,9%</t>
+          <t>7,83%</t>
         </is>
       </c>
       <c r="I29" s="2" t="inlineStr">
         <is>
-          <t>17,54%</t>
+          <t>16,78%</t>
         </is>
       </c>
       <c r="J29" s="2" t="inlineStr">
@@ -7956,12 +7956,12 @@
       </c>
       <c r="L29" s="2" t="inlineStr">
         <is>
-          <t>13364</t>
+          <t>14126</t>
         </is>
       </c>
       <c r="M29" s="2" t="inlineStr">
         <is>
-          <t>27342</t>
+          <t>27397</t>
         </is>
       </c>
       <c r="N29" s="2" t="inlineStr">
@@ -7971,12 +7971,12 @@
       </c>
       <c r="O29" s="2" t="inlineStr">
         <is>
-          <t>9,27%</t>
+          <t>9,8%</t>
         </is>
       </c>
       <c r="P29" s="2" t="inlineStr">
         <is>
-          <t>18,98%</t>
+          <t>19,01%</t>
         </is>
       </c>
       <c r="Q29" s="2" t="inlineStr">
@@ -7991,12 +7991,12 @@
       </c>
       <c r="S29" s="2" t="inlineStr">
         <is>
-          <t>27546</t>
+          <t>27028</t>
         </is>
       </c>
       <c r="T29" s="2" t="inlineStr">
         <is>
-          <t>44704</t>
+          <t>44765</t>
         </is>
       </c>
       <c r="U29" s="2" t="inlineStr">
@@ -8006,12 +8006,12 @@
       </c>
       <c r="V29" s="2" t="inlineStr">
         <is>
-          <t>9,8%</t>
+          <t>9,62%</t>
         </is>
       </c>
       <c r="W29" s="2" t="inlineStr">
         <is>
-          <t>15,91%</t>
+          <t>15,93%</t>
         </is>
       </c>
     </row>
@@ -8034,12 +8034,12 @@
       </c>
       <c r="E30" s="2" t="inlineStr">
         <is>
-          <t>78147</t>
+          <t>77883</t>
         </is>
       </c>
       <c r="F30" s="2" t="inlineStr">
         <is>
-          <t>96653</t>
+          <t>96261</t>
         </is>
       </c>
       <c r="G30" s="2" t="inlineStr">
@@ -8049,12 +8049,12 @@
       </c>
       <c r="H30" s="2" t="inlineStr">
         <is>
-          <t>57,06%</t>
+          <t>56,87%</t>
         </is>
       </c>
       <c r="I30" s="2" t="inlineStr">
         <is>
-          <t>70,58%</t>
+          <t>70,29%</t>
         </is>
       </c>
       <c r="J30" s="2" t="inlineStr">
@@ -8069,12 +8069,12 @@
       </c>
       <c r="L30" s="2" t="inlineStr">
         <is>
-          <t>86164</t>
+          <t>85929</t>
         </is>
       </c>
       <c r="M30" s="2" t="inlineStr">
         <is>
-          <t>105084</t>
+          <t>104400</t>
         </is>
       </c>
       <c r="N30" s="2" t="inlineStr">
@@ -8084,12 +8084,12 @@
       </c>
       <c r="O30" s="2" t="inlineStr">
         <is>
-          <t>59,8%</t>
+          <t>59,63%</t>
         </is>
       </c>
       <c r="P30" s="2" t="inlineStr">
         <is>
-          <t>72,93%</t>
+          <t>72,45%</t>
         </is>
       </c>
       <c r="Q30" s="2" t="inlineStr">
@@ -8104,12 +8104,12 @@
       </c>
       <c r="S30" s="2" t="inlineStr">
         <is>
-          <t>171326</t>
+          <t>171118</t>
         </is>
       </c>
       <c r="T30" s="2" t="inlineStr">
         <is>
-          <t>196958</t>
+          <t>198448</t>
         </is>
       </c>
       <c r="U30" s="2" t="inlineStr">
@@ -8119,12 +8119,12 @@
       </c>
       <c r="V30" s="2" t="inlineStr">
         <is>
-          <t>60,96%</t>
+          <t>60,89%</t>
         </is>
       </c>
       <c r="W30" s="2" t="inlineStr">
         <is>
-          <t>70,08%</t>
+          <t>70,61%</t>
         </is>
       </c>
     </row>
@@ -8264,12 +8264,12 @@
       </c>
       <c r="E32" s="2" t="inlineStr">
         <is>
-          <t>40588</t>
+          <t>42061</t>
         </is>
       </c>
       <c r="F32" s="2" t="inlineStr">
         <is>
-          <t>60386</t>
+          <t>61093</t>
         </is>
       </c>
       <c r="G32" s="2" t="inlineStr">
@@ -8279,12 +8279,12 @@
       </c>
       <c r="H32" s="2" t="inlineStr">
         <is>
-          <t>25,03%</t>
+          <t>25,94%</t>
         </is>
       </c>
       <c r="I32" s="2" t="inlineStr">
         <is>
-          <t>37,24%</t>
+          <t>37,67%</t>
         </is>
       </c>
       <c r="J32" s="2" t="inlineStr">
@@ -8299,12 +8299,12 @@
       </c>
       <c r="L32" s="2" t="inlineStr">
         <is>
-          <t>54741</t>
+          <t>56410</t>
         </is>
       </c>
       <c r="M32" s="2" t="inlineStr">
         <is>
-          <t>75925</t>
+          <t>76129</t>
         </is>
       </c>
       <c r="N32" s="2" t="inlineStr">
@@ -8314,12 +8314,12 @@
       </c>
       <c r="O32" s="2" t="inlineStr">
         <is>
-          <t>32,87%</t>
+          <t>33,87%</t>
         </is>
       </c>
       <c r="P32" s="2" t="inlineStr">
         <is>
-          <t>45,59%</t>
+          <t>45,71%</t>
         </is>
       </c>
       <c r="Q32" s="2" t="inlineStr">
@@ -8334,12 +8334,12 @@
       </c>
       <c r="S32" s="2" t="inlineStr">
         <is>
-          <t>102785</t>
+          <t>103455</t>
         </is>
       </c>
       <c r="T32" s="2" t="inlineStr">
         <is>
-          <t>130358</t>
+          <t>130368</t>
         </is>
       </c>
       <c r="U32" s="2" t="inlineStr">
@@ -8349,7 +8349,7 @@
       </c>
       <c r="V32" s="2" t="inlineStr">
         <is>
-          <t>31,27%</t>
+          <t>31,47%</t>
         </is>
       </c>
       <c r="W32" s="2" t="inlineStr">
@@ -8377,12 +8377,12 @@
       </c>
       <c r="E33" s="2" t="inlineStr">
         <is>
-          <t>13195</t>
+          <t>13705</t>
         </is>
       </c>
       <c r="F33" s="2" t="inlineStr">
         <is>
-          <t>27000</t>
+          <t>27870</t>
         </is>
       </c>
       <c r="G33" s="2" t="inlineStr">
@@ -8392,12 +8392,12 @@
       </c>
       <c r="H33" s="2" t="inlineStr">
         <is>
-          <t>8,14%</t>
+          <t>8,45%</t>
         </is>
       </c>
       <c r="I33" s="2" t="inlineStr">
         <is>
-          <t>16,65%</t>
+          <t>17,19%</t>
         </is>
       </c>
       <c r="J33" s="2" t="inlineStr">
@@ -8412,12 +8412,12 @@
       </c>
       <c r="L33" s="2" t="inlineStr">
         <is>
-          <t>21010</t>
+          <t>20898</t>
         </is>
       </c>
       <c r="M33" s="2" t="inlineStr">
         <is>
-          <t>37750</t>
+          <t>36207</t>
         </is>
       </c>
       <c r="N33" s="2" t="inlineStr">
@@ -8427,12 +8427,12 @@
       </c>
       <c r="O33" s="2" t="inlineStr">
         <is>
-          <t>12,62%</t>
+          <t>12,55%</t>
         </is>
       </c>
       <c r="P33" s="2" t="inlineStr">
         <is>
-          <t>22,67%</t>
+          <t>21,74%</t>
         </is>
       </c>
       <c r="Q33" s="2" t="inlineStr">
@@ -8447,12 +8447,12 @@
       </c>
       <c r="S33" s="2" t="inlineStr">
         <is>
-          <t>37996</t>
+          <t>38452</t>
         </is>
       </c>
       <c r="T33" s="2" t="inlineStr">
         <is>
-          <t>59839</t>
+          <t>58685</t>
         </is>
       </c>
       <c r="U33" s="2" t="inlineStr">
@@ -8462,12 +8462,12 @@
       </c>
       <c r="V33" s="2" t="inlineStr">
         <is>
-          <t>11,56%</t>
+          <t>11,7%</t>
         </is>
       </c>
       <c r="W33" s="2" t="inlineStr">
         <is>
-          <t>18,2%</t>
+          <t>17,85%</t>
         </is>
       </c>
     </row>
@@ -8490,12 +8490,12 @@
       </c>
       <c r="E34" s="2" t="inlineStr">
         <is>
-          <t>81542</t>
+          <t>80586</t>
         </is>
       </c>
       <c r="F34" s="2" t="inlineStr">
         <is>
-          <t>101894</t>
+          <t>101369</t>
         </is>
       </c>
       <c r="G34" s="2" t="inlineStr">
@@ -8505,12 +8505,12 @@
       </c>
       <c r="H34" s="2" t="inlineStr">
         <is>
-          <t>50,28%</t>
+          <t>49,69%</t>
         </is>
       </c>
       <c r="I34" s="2" t="inlineStr">
         <is>
-          <t>62,83%</t>
+          <t>62,51%</t>
         </is>
       </c>
       <c r="J34" s="2" t="inlineStr">
@@ -8525,12 +8525,12 @@
       </c>
       <c r="L34" s="2" t="inlineStr">
         <is>
-          <t>62396</t>
+          <t>63194</t>
         </is>
       </c>
       <c r="M34" s="2" t="inlineStr">
         <is>
-          <t>82976</t>
+          <t>82908</t>
         </is>
       </c>
       <c r="N34" s="2" t="inlineStr">
@@ -8540,12 +8540,12 @@
       </c>
       <c r="O34" s="2" t="inlineStr">
         <is>
-          <t>37,47%</t>
+          <t>37,95%</t>
         </is>
       </c>
       <c r="P34" s="2" t="inlineStr">
         <is>
-          <t>49,83%</t>
+          <t>49,79%</t>
         </is>
       </c>
       <c r="Q34" s="2" t="inlineStr">
@@ -8560,12 +8560,12 @@
       </c>
       <c r="S34" s="2" t="inlineStr">
         <is>
-          <t>149525</t>
+          <t>150921</t>
         </is>
       </c>
       <c r="T34" s="2" t="inlineStr">
         <is>
-          <t>179251</t>
+          <t>179853</t>
         </is>
       </c>
       <c r="U34" s="2" t="inlineStr">
@@ -8575,12 +8575,12 @@
       </c>
       <c r="V34" s="2" t="inlineStr">
         <is>
-          <t>45,49%</t>
+          <t>45,91%</t>
         </is>
       </c>
       <c r="W34" s="2" t="inlineStr">
         <is>
-          <t>54,53%</t>
+          <t>54,72%</t>
         </is>
       </c>
     </row>
@@ -8720,12 +8720,12 @@
       </c>
       <c r="E36" s="2" t="inlineStr">
         <is>
-          <t>182270</t>
+          <t>183510</t>
         </is>
       </c>
       <c r="F36" s="2" t="inlineStr">
         <is>
-          <t>219449</t>
+          <t>222753</t>
         </is>
       </c>
       <c r="G36" s="2" t="inlineStr">
@@ -8735,12 +8735,12 @@
       </c>
       <c r="H36" s="2" t="inlineStr">
         <is>
-          <t>25,95%</t>
+          <t>26,13%</t>
         </is>
       </c>
       <c r="I36" s="2" t="inlineStr">
         <is>
-          <t>31,24%</t>
+          <t>31,72%</t>
         </is>
       </c>
       <c r="J36" s="2" t="inlineStr">
@@ -8755,12 +8755,12 @@
       </c>
       <c r="L36" s="2" t="inlineStr">
         <is>
-          <t>212118</t>
+          <t>214237</t>
         </is>
       </c>
       <c r="M36" s="2" t="inlineStr">
         <is>
-          <t>254953</t>
+          <t>253551</t>
         </is>
       </c>
       <c r="N36" s="2" t="inlineStr">
@@ -8770,12 +8770,12 @@
       </c>
       <c r="O36" s="2" t="inlineStr">
         <is>
-          <t>28,7%</t>
+          <t>28,98%</t>
         </is>
       </c>
       <c r="P36" s="2" t="inlineStr">
         <is>
-          <t>34,49%</t>
+          <t>34,3%</t>
         </is>
       </c>
       <c r="Q36" s="2" t="inlineStr">
@@ -8790,12 +8790,12 @@
       </c>
       <c r="S36" s="2" t="inlineStr">
         <is>
-          <t>407196</t>
+          <t>409343</t>
         </is>
       </c>
       <c r="T36" s="2" t="inlineStr">
         <is>
-          <t>463469</t>
+          <t>464516</t>
         </is>
       </c>
       <c r="U36" s="2" t="inlineStr">
@@ -8805,12 +8805,12 @@
       </c>
       <c r="V36" s="2" t="inlineStr">
         <is>
-          <t>28,25%</t>
+          <t>28,4%</t>
         </is>
       </c>
       <c r="W36" s="2" t="inlineStr">
         <is>
-          <t>32,15%</t>
+          <t>32,22%</t>
         </is>
       </c>
     </row>
@@ -8833,12 +8833,12 @@
       </c>
       <c r="E37" s="2" t="inlineStr">
         <is>
-          <t>66985</t>
+          <t>68087</t>
         </is>
       </c>
       <c r="F37" s="2" t="inlineStr">
         <is>
-          <t>94218</t>
+          <t>95181</t>
         </is>
       </c>
       <c r="G37" s="2" t="inlineStr">
@@ -8848,12 +8848,12 @@
       </c>
       <c r="H37" s="2" t="inlineStr">
         <is>
-          <t>9,54%</t>
+          <t>9,69%</t>
         </is>
       </c>
       <c r="I37" s="2" t="inlineStr">
         <is>
-          <t>13,41%</t>
+          <t>13,55%</t>
         </is>
       </c>
       <c r="J37" s="2" t="inlineStr">
@@ -8868,12 +8868,12 @@
       </c>
       <c r="L37" s="2" t="inlineStr">
         <is>
-          <t>77089</t>
+          <t>78072</t>
         </is>
       </c>
       <c r="M37" s="2" t="inlineStr">
         <is>
-          <t>107160</t>
+          <t>106403</t>
         </is>
       </c>
       <c r="N37" s="2" t="inlineStr">
@@ -8883,12 +8883,12 @@
       </c>
       <c r="O37" s="2" t="inlineStr">
         <is>
-          <t>10,43%</t>
+          <t>10,56%</t>
         </is>
       </c>
       <c r="P37" s="2" t="inlineStr">
         <is>
-          <t>14,5%</t>
+          <t>14,4%</t>
         </is>
       </c>
       <c r="Q37" s="2" t="inlineStr">
@@ -8903,12 +8903,12 @@
       </c>
       <c r="S37" s="2" t="inlineStr">
         <is>
-          <t>152899</t>
+          <t>155473</t>
         </is>
       </c>
       <c r="T37" s="2" t="inlineStr">
         <is>
-          <t>193067</t>
+          <t>194805</t>
         </is>
       </c>
       <c r="U37" s="2" t="inlineStr">
@@ -8918,12 +8918,12 @@
       </c>
       <c r="V37" s="2" t="inlineStr">
         <is>
-          <t>10,61%</t>
+          <t>10,79%</t>
         </is>
       </c>
       <c r="W37" s="2" t="inlineStr">
         <is>
-          <t>13,39%</t>
+          <t>13,51%</t>
         </is>
       </c>
     </row>
@@ -8946,12 +8946,12 @@
       </c>
       <c r="E38" s="2" t="inlineStr">
         <is>
-          <t>398306</t>
+          <t>398049</t>
         </is>
       </c>
       <c r="F38" s="2" t="inlineStr">
         <is>
-          <t>440979</t>
+          <t>441660</t>
         </is>
       </c>
       <c r="G38" s="2" t="inlineStr">
@@ -8961,12 +8961,12 @@
       </c>
       <c r="H38" s="2" t="inlineStr">
         <is>
-          <t>56,71%</t>
+          <t>56,67%</t>
         </is>
       </c>
       <c r="I38" s="2" t="inlineStr">
         <is>
-          <t>62,79%</t>
+          <t>62,88%</t>
         </is>
       </c>
       <c r="J38" s="2" t="inlineStr">
@@ -8981,12 +8981,12 @@
       </c>
       <c r="L38" s="2" t="inlineStr">
         <is>
-          <t>391947</t>
+          <t>393101</t>
         </is>
       </c>
       <c r="M38" s="2" t="inlineStr">
         <is>
-          <t>439168</t>
+          <t>436109</t>
         </is>
       </c>
       <c r="N38" s="2" t="inlineStr">
@@ -8996,12 +8996,12 @@
       </c>
       <c r="O38" s="2" t="inlineStr">
         <is>
-          <t>53,03%</t>
+          <t>53,18%</t>
         </is>
       </c>
       <c r="P38" s="2" t="inlineStr">
         <is>
-          <t>59,42%</t>
+          <t>59,0%</t>
         </is>
       </c>
       <c r="Q38" s="2" t="inlineStr">
@@ -9016,12 +9016,12 @@
       </c>
       <c r="S38" s="2" t="inlineStr">
         <is>
-          <t>802360</t>
+          <t>802786</t>
         </is>
       </c>
       <c r="T38" s="2" t="inlineStr">
         <is>
-          <t>861957</t>
+          <t>865015</t>
         </is>
       </c>
       <c r="U38" s="2" t="inlineStr">
@@ -9031,12 +9031,12 @@
       </c>
       <c r="V38" s="2" t="inlineStr">
         <is>
-          <t>55,66%</t>
+          <t>55,69%</t>
         </is>
       </c>
       <c r="W38" s="2" t="inlineStr">
         <is>
-          <t>59,8%</t>
+          <t>60,01%</t>
         </is>
       </c>
     </row>
@@ -9412,12 +9412,12 @@
       </c>
       <c r="E4" s="2" t="inlineStr">
         <is>
-          <t>12005</t>
+          <t>11574</t>
         </is>
       </c>
       <c r="F4" s="2" t="inlineStr">
         <is>
-          <t>22837</t>
+          <t>22763</t>
         </is>
       </c>
       <c r="G4" s="2" t="inlineStr">
@@ -9427,12 +9427,12 @@
       </c>
       <c r="H4" s="2" t="inlineStr">
         <is>
-          <t>20,93%</t>
+          <t>20,17%</t>
         </is>
       </c>
       <c r="I4" s="2" t="inlineStr">
         <is>
-          <t>39,81%</t>
+          <t>39,68%</t>
         </is>
       </c>
       <c r="J4" s="2" t="inlineStr">
@@ -9447,12 +9447,12 @@
       </c>
       <c r="L4" s="2" t="inlineStr">
         <is>
-          <t>11239</t>
+          <t>11402</t>
         </is>
       </c>
       <c r="M4" s="2" t="inlineStr">
         <is>
-          <t>22771</t>
+          <t>22871</t>
         </is>
       </c>
       <c r="N4" s="2" t="inlineStr">
@@ -9462,12 +9462,12 @@
       </c>
       <c r="O4" s="2" t="inlineStr">
         <is>
-          <t>17,62%</t>
+          <t>17,88%</t>
         </is>
       </c>
       <c r="P4" s="2" t="inlineStr">
         <is>
-          <t>35,71%</t>
+          <t>35,86%</t>
         </is>
       </c>
       <c r="Q4" s="2" t="inlineStr">
@@ -9482,12 +9482,12 @@
       </c>
       <c r="S4" s="2" t="inlineStr">
         <is>
-          <t>26206</t>
+          <t>26181</t>
         </is>
       </c>
       <c r="T4" s="2" t="inlineStr">
         <is>
-          <t>41972</t>
+          <t>41386</t>
         </is>
       </c>
       <c r="U4" s="2" t="inlineStr">
@@ -9497,12 +9497,12 @@
       </c>
       <c r="V4" s="2" t="inlineStr">
         <is>
-          <t>21,63%</t>
+          <t>21,61%</t>
         </is>
       </c>
       <c r="W4" s="2" t="inlineStr">
         <is>
-          <t>34,65%</t>
+          <t>34,16%</t>
         </is>
       </c>
     </row>
@@ -9525,12 +9525,12 @@
       </c>
       <c r="E5" s="2" t="inlineStr">
         <is>
-          <t>1100</t>
+          <t>1123</t>
         </is>
       </c>
       <c r="F5" s="2" t="inlineStr">
         <is>
-          <t>6369</t>
+          <t>6595</t>
         </is>
       </c>
       <c r="G5" s="2" t="inlineStr">
@@ -9540,12 +9540,12 @@
       </c>
       <c r="H5" s="2" t="inlineStr">
         <is>
-          <t>1,92%</t>
+          <t>1,96%</t>
         </is>
       </c>
       <c r="I5" s="2" t="inlineStr">
         <is>
-          <t>11,1%</t>
+          <t>11,49%</t>
         </is>
       </c>
       <c r="J5" s="2" t="inlineStr">
@@ -9560,12 +9560,12 @@
       </c>
       <c r="L5" s="2" t="inlineStr">
         <is>
-          <t>1456</t>
+          <t>1433</t>
         </is>
       </c>
       <c r="M5" s="2" t="inlineStr">
         <is>
-          <t>8373</t>
+          <t>7979</t>
         </is>
       </c>
       <c r="N5" s="2" t="inlineStr">
@@ -9575,12 +9575,12 @@
       </c>
       <c r="O5" s="2" t="inlineStr">
         <is>
-          <t>2,28%</t>
+          <t>2,25%</t>
         </is>
       </c>
       <c r="P5" s="2" t="inlineStr">
         <is>
-          <t>13,13%</t>
+          <t>12,51%</t>
         </is>
       </c>
       <c r="Q5" s="2" t="inlineStr">
@@ -9595,12 +9595,12 @@
       </c>
       <c r="S5" s="2" t="inlineStr">
         <is>
-          <t>3856</t>
+          <t>3908</t>
         </is>
       </c>
       <c r="T5" s="2" t="inlineStr">
         <is>
-          <t>12717</t>
+          <t>11851</t>
         </is>
       </c>
       <c r="U5" s="2" t="inlineStr">
@@ -9610,12 +9610,12 @@
       </c>
       <c r="V5" s="2" t="inlineStr">
         <is>
-          <t>3,18%</t>
+          <t>3,23%</t>
         </is>
       </c>
       <c r="W5" s="2" t="inlineStr">
         <is>
-          <t>10,5%</t>
+          <t>9,78%</t>
         </is>
       </c>
     </row>
@@ -9638,12 +9638,12 @@
       </c>
       <c r="E6" s="2" t="inlineStr">
         <is>
-          <t>31228</t>
+          <t>31279</t>
         </is>
       </c>
       <c r="F6" s="2" t="inlineStr">
         <is>
-          <t>42648</t>
+          <t>42904</t>
         </is>
       </c>
       <c r="G6" s="2" t="inlineStr">
@@ -9653,12 +9653,12 @@
       </c>
       <c r="H6" s="2" t="inlineStr">
         <is>
-          <t>54,43%</t>
+          <t>54,52%</t>
         </is>
       </c>
       <c r="I6" s="2" t="inlineStr">
         <is>
-          <t>74,34%</t>
+          <t>74,78%</t>
         </is>
       </c>
       <c r="J6" s="2" t="inlineStr">
@@ -9673,12 +9673,12 @@
       </c>
       <c r="L6" s="2" t="inlineStr">
         <is>
-          <t>37028</t>
+          <t>36875</t>
         </is>
       </c>
       <c r="M6" s="2" t="inlineStr">
         <is>
-          <t>49002</t>
+          <t>48577</t>
         </is>
       </c>
       <c r="N6" s="2" t="inlineStr">
@@ -9688,12 +9688,12 @@
       </c>
       <c r="O6" s="2" t="inlineStr">
         <is>
-          <t>58,06%</t>
+          <t>57,83%</t>
         </is>
       </c>
       <c r="P6" s="2" t="inlineStr">
         <is>
-          <t>76,84%</t>
+          <t>76,18%</t>
         </is>
       </c>
       <c r="Q6" s="2" t="inlineStr">
@@ -9708,12 +9708,12 @@
       </c>
       <c r="S6" s="2" t="inlineStr">
         <is>
-          <t>71640</t>
+          <t>71609</t>
         </is>
       </c>
       <c r="T6" s="2" t="inlineStr">
         <is>
-          <t>88897</t>
+          <t>88492</t>
         </is>
       </c>
       <c r="U6" s="2" t="inlineStr">
@@ -9723,12 +9723,12 @@
       </c>
       <c r="V6" s="2" t="inlineStr">
         <is>
-          <t>59,14%</t>
+          <t>59,11%</t>
         </is>
       </c>
       <c r="W6" s="2" t="inlineStr">
         <is>
-          <t>73,38%</t>
+          <t>73,05%</t>
         </is>
       </c>
     </row>
@@ -9868,12 +9868,12 @@
       </c>
       <c r="E8" s="2" t="inlineStr">
         <is>
-          <t>30930</t>
+          <t>30935</t>
         </is>
       </c>
       <c r="F8" s="2" t="inlineStr">
         <is>
-          <t>46926</t>
+          <t>46727</t>
         </is>
       </c>
       <c r="G8" s="2" t="inlineStr">
@@ -9888,7 +9888,7 @@
       </c>
       <c r="I8" s="2" t="inlineStr">
         <is>
-          <t>45,65%</t>
+          <t>45,45%</t>
         </is>
       </c>
       <c r="J8" s="2" t="inlineStr">
@@ -9903,12 +9903,12 @@
       </c>
       <c r="L8" s="2" t="inlineStr">
         <is>
-          <t>24987</t>
+          <t>24232</t>
         </is>
       </c>
       <c r="M8" s="2" t="inlineStr">
         <is>
-          <t>40258</t>
+          <t>40115</t>
         </is>
       </c>
       <c r="N8" s="2" t="inlineStr">
@@ -9918,12 +9918,12 @@
       </c>
       <c r="O8" s="2" t="inlineStr">
         <is>
-          <t>23,07%</t>
+          <t>22,37%</t>
         </is>
       </c>
       <c r="P8" s="2" t="inlineStr">
         <is>
-          <t>37,17%</t>
+          <t>37,03%</t>
         </is>
       </c>
       <c r="Q8" s="2" t="inlineStr">
@@ -9938,12 +9938,12 @@
       </c>
       <c r="S8" s="2" t="inlineStr">
         <is>
-          <t>60501</t>
+          <t>60008</t>
         </is>
       </c>
       <c r="T8" s="2" t="inlineStr">
         <is>
-          <t>83512</t>
+          <t>81905</t>
         </is>
       </c>
       <c r="U8" s="2" t="inlineStr">
@@ -9953,12 +9953,12 @@
       </c>
       <c r="V8" s="2" t="inlineStr">
         <is>
-          <t>28,66%</t>
+          <t>28,42%</t>
         </is>
       </c>
       <c r="W8" s="2" t="inlineStr">
         <is>
-          <t>39,56%</t>
+          <t>38,79%</t>
         </is>
       </c>
     </row>
@@ -9981,12 +9981,12 @@
       </c>
       <c r="E9" s="2" t="inlineStr">
         <is>
-          <t>5000</t>
+          <t>5049</t>
         </is>
       </c>
       <c r="F9" s="2" t="inlineStr">
         <is>
-          <t>13680</t>
+          <t>13965</t>
         </is>
       </c>
       <c r="G9" s="2" t="inlineStr">
@@ -9996,12 +9996,12 @@
       </c>
       <c r="H9" s="2" t="inlineStr">
         <is>
-          <t>4,86%</t>
+          <t>4,91%</t>
         </is>
       </c>
       <c r="I9" s="2" t="inlineStr">
         <is>
-          <t>13,31%</t>
+          <t>13,58%</t>
         </is>
       </c>
       <c r="J9" s="2" t="inlineStr">
@@ -10016,12 +10016,12 @@
       </c>
       <c r="L9" s="2" t="inlineStr">
         <is>
-          <t>6146</t>
+          <t>6088</t>
         </is>
       </c>
       <c r="M9" s="2" t="inlineStr">
         <is>
-          <t>16449</t>
+          <t>16342</t>
         </is>
       </c>
       <c r="N9" s="2" t="inlineStr">
@@ -10031,12 +10031,12 @@
       </c>
       <c r="O9" s="2" t="inlineStr">
         <is>
-          <t>5,67%</t>
+          <t>5,62%</t>
         </is>
       </c>
       <c r="P9" s="2" t="inlineStr">
         <is>
-          <t>15,19%</t>
+          <t>15,09%</t>
         </is>
       </c>
       <c r="Q9" s="2" t="inlineStr">
@@ -10051,12 +10051,12 @@
       </c>
       <c r="S9" s="2" t="inlineStr">
         <is>
-          <t>12834</t>
+          <t>13393</t>
         </is>
       </c>
       <c r="T9" s="2" t="inlineStr">
         <is>
-          <t>25559</t>
+          <t>26335</t>
         </is>
       </c>
       <c r="U9" s="2" t="inlineStr">
@@ -10066,12 +10066,12 @@
       </c>
       <c r="V9" s="2" t="inlineStr">
         <is>
-          <t>6,08%</t>
+          <t>6,34%</t>
         </is>
       </c>
       <c r="W9" s="2" t="inlineStr">
         <is>
-          <t>12,11%</t>
+          <t>12,47%</t>
         </is>
       </c>
     </row>
@@ -10094,12 +10094,12 @@
       </c>
       <c r="E10" s="2" t="inlineStr">
         <is>
-          <t>46562</t>
+          <t>47230</t>
         </is>
       </c>
       <c r="F10" s="2" t="inlineStr">
         <is>
-          <t>63470</t>
+          <t>63393</t>
         </is>
       </c>
       <c r="G10" s="2" t="inlineStr">
@@ -10109,12 +10109,12 @@
       </c>
       <c r="H10" s="2" t="inlineStr">
         <is>
-          <t>45,29%</t>
+          <t>45,94%</t>
         </is>
       </c>
       <c r="I10" s="2" t="inlineStr">
         <is>
-          <t>61,74%</t>
+          <t>61,66%</t>
         </is>
       </c>
       <c r="J10" s="2" t="inlineStr">
@@ -10129,12 +10129,12 @@
       </c>
       <c r="L10" s="2" t="inlineStr">
         <is>
-          <t>57743</t>
+          <t>57645</t>
         </is>
       </c>
       <c r="M10" s="2" t="inlineStr">
         <is>
-          <t>74781</t>
+          <t>74405</t>
         </is>
       </c>
       <c r="N10" s="2" t="inlineStr">
@@ -10144,12 +10144,12 @@
       </c>
       <c r="O10" s="2" t="inlineStr">
         <is>
-          <t>53,31%</t>
+          <t>53,22%</t>
         </is>
       </c>
       <c r="P10" s="2" t="inlineStr">
         <is>
-          <t>69,04%</t>
+          <t>68,69%</t>
         </is>
       </c>
       <c r="Q10" s="2" t="inlineStr">
@@ -10164,12 +10164,12 @@
       </c>
       <c r="S10" s="2" t="inlineStr">
         <is>
-          <t>109388</t>
+          <t>110212</t>
         </is>
       </c>
       <c r="T10" s="2" t="inlineStr">
         <is>
-          <t>133322</t>
+          <t>133879</t>
         </is>
       </c>
       <c r="U10" s="2" t="inlineStr">
@@ -10179,12 +10179,12 @@
       </c>
       <c r="V10" s="2" t="inlineStr">
         <is>
-          <t>51,81%</t>
+          <t>52,2%</t>
         </is>
       </c>
       <c r="W10" s="2" t="inlineStr">
         <is>
-          <t>63,15%</t>
+          <t>63,41%</t>
         </is>
       </c>
     </row>
@@ -10324,12 +10324,12 @@
       </c>
       <c r="E12" s="2" t="inlineStr">
         <is>
-          <t>4488</t>
+          <t>4681</t>
         </is>
       </c>
       <c r="F12" s="2" t="inlineStr">
         <is>
-          <t>14967</t>
+          <t>14331</t>
         </is>
       </c>
       <c r="G12" s="2" t="inlineStr">
@@ -10339,12 +10339,12 @@
       </c>
       <c r="H12" s="2" t="inlineStr">
         <is>
-          <t>6,8%</t>
+          <t>7,09%</t>
         </is>
       </c>
       <c r="I12" s="2" t="inlineStr">
         <is>
-          <t>22,68%</t>
+          <t>21,72%</t>
         </is>
       </c>
       <c r="J12" s="2" t="inlineStr">
@@ -10359,12 +10359,12 @@
       </c>
       <c r="L12" s="2" t="inlineStr">
         <is>
-          <t>6508</t>
+          <t>6289</t>
         </is>
       </c>
       <c r="M12" s="2" t="inlineStr">
         <is>
-          <t>16592</t>
+          <t>16243</t>
         </is>
       </c>
       <c r="N12" s="2" t="inlineStr">
@@ -10374,12 +10374,12 @@
       </c>
       <c r="O12" s="2" t="inlineStr">
         <is>
-          <t>9,59%</t>
+          <t>9,27%</t>
         </is>
       </c>
       <c r="P12" s="2" t="inlineStr">
         <is>
-          <t>24,45%</t>
+          <t>23,94%</t>
         </is>
       </c>
       <c r="Q12" s="2" t="inlineStr">
@@ -10394,12 +10394,12 @@
       </c>
       <c r="S12" s="2" t="inlineStr">
         <is>
-          <t>13669</t>
+          <t>13312</t>
         </is>
       </c>
       <c r="T12" s="2" t="inlineStr">
         <is>
-          <t>26709</t>
+          <t>27661</t>
         </is>
       </c>
       <c r="U12" s="2" t="inlineStr">
@@ -10409,12 +10409,12 @@
       </c>
       <c r="V12" s="2" t="inlineStr">
         <is>
-          <t>10,21%</t>
+          <t>9,95%</t>
         </is>
       </c>
       <c r="W12" s="2" t="inlineStr">
         <is>
-          <t>19,96%</t>
+          <t>20,67%</t>
         </is>
       </c>
     </row>
@@ -10437,12 +10437,12 @@
       </c>
       <c r="E13" s="2" t="inlineStr">
         <is>
-          <t>3865</t>
+          <t>3391</t>
         </is>
       </c>
       <c r="F13" s="2" t="inlineStr">
         <is>
-          <t>13001</t>
+          <t>12304</t>
         </is>
       </c>
       <c r="G13" s="2" t="inlineStr">
@@ -10452,12 +10452,12 @@
       </c>
       <c r="H13" s="2" t="inlineStr">
         <is>
-          <t>5,86%</t>
+          <t>5,14%</t>
         </is>
       </c>
       <c r="I13" s="2" t="inlineStr">
         <is>
-          <t>19,7%</t>
+          <t>18,64%</t>
         </is>
       </c>
       <c r="J13" s="2" t="inlineStr">
@@ -10472,12 +10472,12 @@
       </c>
       <c r="L13" s="2" t="inlineStr">
         <is>
-          <t>4232</t>
+          <t>3738</t>
         </is>
       </c>
       <c r="M13" s="2" t="inlineStr">
         <is>
-          <t>13050</t>
+          <t>12985</t>
         </is>
       </c>
       <c r="N13" s="2" t="inlineStr">
@@ -10487,12 +10487,12 @@
       </c>
       <c r="O13" s="2" t="inlineStr">
         <is>
-          <t>6,24%</t>
+          <t>5,51%</t>
         </is>
       </c>
       <c r="P13" s="2" t="inlineStr">
         <is>
-          <t>19,23%</t>
+          <t>19,14%</t>
         </is>
       </c>
       <c r="Q13" s="2" t="inlineStr">
@@ -10507,12 +10507,12 @@
       </c>
       <c r="S13" s="2" t="inlineStr">
         <is>
-          <t>9178</t>
+          <t>9794</t>
         </is>
       </c>
       <c r="T13" s="2" t="inlineStr">
         <is>
-          <t>21887</t>
+          <t>22708</t>
         </is>
       </c>
       <c r="U13" s="2" t="inlineStr">
@@ -10522,12 +10522,12 @@
       </c>
       <c r="V13" s="2" t="inlineStr">
         <is>
-          <t>6,86%</t>
+          <t>7,32%</t>
         </is>
       </c>
       <c r="W13" s="2" t="inlineStr">
         <is>
-          <t>16,35%</t>
+          <t>16,97%</t>
         </is>
       </c>
     </row>
@@ -10550,12 +10550,12 @@
       </c>
       <c r="E14" s="2" t="inlineStr">
         <is>
-          <t>42932</t>
+          <t>43485</t>
         </is>
       </c>
       <c r="F14" s="2" t="inlineStr">
         <is>
-          <t>55147</t>
+          <t>55602</t>
         </is>
       </c>
       <c r="G14" s="2" t="inlineStr">
@@ -10565,12 +10565,12 @@
       </c>
       <c r="H14" s="2" t="inlineStr">
         <is>
-          <t>65,05%</t>
+          <t>65,89%</t>
         </is>
       </c>
       <c r="I14" s="2" t="inlineStr">
         <is>
-          <t>83,56%</t>
+          <t>84,25%</t>
         </is>
       </c>
       <c r="J14" s="2" t="inlineStr">
@@ -10585,12 +10585,12 @@
       </c>
       <c r="L14" s="2" t="inlineStr">
         <is>
-          <t>42933</t>
+          <t>42865</t>
         </is>
       </c>
       <c r="M14" s="2" t="inlineStr">
         <is>
-          <t>54444</t>
+          <t>55415</t>
         </is>
       </c>
       <c r="N14" s="2" t="inlineStr">
@@ -10600,12 +10600,12 @@
       </c>
       <c r="O14" s="2" t="inlineStr">
         <is>
-          <t>63,28%</t>
+          <t>63,18%</t>
         </is>
       </c>
       <c r="P14" s="2" t="inlineStr">
         <is>
-          <t>80,24%</t>
+          <t>81,68%</t>
         </is>
       </c>
       <c r="Q14" s="2" t="inlineStr">
@@ -10620,12 +10620,12 @@
       </c>
       <c r="S14" s="2" t="inlineStr">
         <is>
-          <t>90451</t>
+          <t>90360</t>
         </is>
       </c>
       <c r="T14" s="2" t="inlineStr">
         <is>
-          <t>107264</t>
+          <t>107788</t>
         </is>
       </c>
       <c r="U14" s="2" t="inlineStr">
@@ -10635,12 +10635,12 @@
       </c>
       <c r="V14" s="2" t="inlineStr">
         <is>
-          <t>67,58%</t>
+          <t>67,51%</t>
         </is>
       </c>
       <c r="W14" s="2" t="inlineStr">
         <is>
-          <t>80,14%</t>
+          <t>80,53%</t>
         </is>
       </c>
     </row>
@@ -10780,12 +10780,12 @@
       </c>
       <c r="E16" s="2" t="inlineStr">
         <is>
-          <t>11437</t>
+          <t>11067</t>
         </is>
       </c>
       <c r="F16" s="2" t="inlineStr">
         <is>
-          <t>23752</t>
+          <t>23790</t>
         </is>
       </c>
       <c r="G16" s="2" t="inlineStr">
@@ -10795,12 +10795,12 @@
       </c>
       <c r="H16" s="2" t="inlineStr">
         <is>
-          <t>15,09%</t>
+          <t>14,6%</t>
         </is>
       </c>
       <c r="I16" s="2" t="inlineStr">
         <is>
-          <t>31,34%</t>
+          <t>31,39%</t>
         </is>
       </c>
       <c r="J16" s="2" t="inlineStr">
@@ -10815,12 +10815,12 @@
       </c>
       <c r="L16" s="2" t="inlineStr">
         <is>
-          <t>15499</t>
+          <t>15453</t>
         </is>
       </c>
       <c r="M16" s="2" t="inlineStr">
         <is>
-          <t>28734</t>
+          <t>29546</t>
         </is>
       </c>
       <c r="N16" s="2" t="inlineStr">
@@ -10830,12 +10830,12 @@
       </c>
       <c r="O16" s="2" t="inlineStr">
         <is>
-          <t>19,4%</t>
+          <t>19,35%</t>
         </is>
       </c>
       <c r="P16" s="2" t="inlineStr">
         <is>
-          <t>35,97%</t>
+          <t>36,99%</t>
         </is>
       </c>
       <c r="Q16" s="2" t="inlineStr">
@@ -10850,12 +10850,12 @@
       </c>
       <c r="S16" s="2" t="inlineStr">
         <is>
-          <t>30183</t>
+          <t>30285</t>
         </is>
       </c>
       <c r="T16" s="2" t="inlineStr">
         <is>
-          <t>47876</t>
+          <t>47719</t>
         </is>
       </c>
       <c r="U16" s="2" t="inlineStr">
@@ -10865,12 +10865,12 @@
       </c>
       <c r="V16" s="2" t="inlineStr">
         <is>
-          <t>19,39%</t>
+          <t>19,46%</t>
         </is>
       </c>
       <c r="W16" s="2" t="inlineStr">
         <is>
-          <t>30,76%</t>
+          <t>30,66%</t>
         </is>
       </c>
     </row>
@@ -10893,12 +10893,12 @@
       </c>
       <c r="E17" s="2" t="inlineStr">
         <is>
-          <t>1809</t>
+          <t>1774</t>
         </is>
       </c>
       <c r="F17" s="2" t="inlineStr">
         <is>
-          <t>9200</t>
+          <t>9406</t>
         </is>
       </c>
       <c r="G17" s="2" t="inlineStr">
@@ -10908,12 +10908,12 @@
       </c>
       <c r="H17" s="2" t="inlineStr">
         <is>
-          <t>2,39%</t>
+          <t>2,34%</t>
         </is>
       </c>
       <c r="I17" s="2" t="inlineStr">
         <is>
-          <t>12,14%</t>
+          <t>12,41%</t>
         </is>
       </c>
       <c r="J17" s="2" t="inlineStr">
@@ -10928,12 +10928,12 @@
       </c>
       <c r="L17" s="2" t="inlineStr">
         <is>
-          <t>1726</t>
+          <t>2017</t>
         </is>
       </c>
       <c r="M17" s="2" t="inlineStr">
         <is>
-          <t>10166</t>
+          <t>9872</t>
         </is>
       </c>
       <c r="N17" s="2" t="inlineStr">
@@ -10943,12 +10943,12 @@
       </c>
       <c r="O17" s="2" t="inlineStr">
         <is>
-          <t>2,16%</t>
+          <t>2,53%</t>
         </is>
       </c>
       <c r="P17" s="2" t="inlineStr">
         <is>
-          <t>12,73%</t>
+          <t>12,36%</t>
         </is>
       </c>
       <c r="Q17" s="2" t="inlineStr">
@@ -10963,12 +10963,12 @@
       </c>
       <c r="S17" s="2" t="inlineStr">
         <is>
-          <t>4725</t>
+          <t>5200</t>
         </is>
       </c>
       <c r="T17" s="2" t="inlineStr">
         <is>
-          <t>15086</t>
+          <t>15105</t>
         </is>
       </c>
       <c r="U17" s="2" t="inlineStr">
@@ -10978,12 +10978,12 @@
       </c>
       <c r="V17" s="2" t="inlineStr">
         <is>
-          <t>3,04%</t>
+          <t>3,34%</t>
         </is>
       </c>
       <c r="W17" s="2" t="inlineStr">
         <is>
-          <t>9,69%</t>
+          <t>9,7%</t>
         </is>
       </c>
     </row>
@@ -11006,12 +11006,12 @@
       </c>
       <c r="E18" s="2" t="inlineStr">
         <is>
-          <t>47833</t>
+          <t>47458</t>
         </is>
       </c>
       <c r="F18" s="2" t="inlineStr">
         <is>
-          <t>60929</t>
+          <t>61148</t>
         </is>
       </c>
       <c r="G18" s="2" t="inlineStr">
@@ -11021,12 +11021,12 @@
       </c>
       <c r="H18" s="2" t="inlineStr">
         <is>
-          <t>63,12%</t>
+          <t>62,63%</t>
         </is>
       </c>
       <c r="I18" s="2" t="inlineStr">
         <is>
-          <t>80,4%</t>
+          <t>80,69%</t>
         </is>
       </c>
       <c r="J18" s="2" t="inlineStr">
@@ -11041,12 +11041,12 @@
       </c>
       <c r="L18" s="2" t="inlineStr">
         <is>
-          <t>46121</t>
+          <t>45898</t>
         </is>
       </c>
       <c r="M18" s="2" t="inlineStr">
         <is>
-          <t>60643</t>
+          <t>60109</t>
         </is>
       </c>
       <c r="N18" s="2" t="inlineStr">
@@ -11056,12 +11056,12 @@
       </c>
       <c r="O18" s="2" t="inlineStr">
         <is>
-          <t>57,74%</t>
+          <t>57,46%</t>
         </is>
       </c>
       <c r="P18" s="2" t="inlineStr">
         <is>
-          <t>75,92%</t>
+          <t>75,25%</t>
         </is>
       </c>
       <c r="Q18" s="2" t="inlineStr">
@@ -11076,12 +11076,12 @@
       </c>
       <c r="S18" s="2" t="inlineStr">
         <is>
-          <t>98690</t>
+          <t>99290</t>
         </is>
       </c>
       <c r="T18" s="2" t="inlineStr">
         <is>
-          <t>117265</t>
+          <t>117894</t>
         </is>
       </c>
       <c r="U18" s="2" t="inlineStr">
@@ -11091,12 +11091,12 @@
       </c>
       <c r="V18" s="2" t="inlineStr">
         <is>
-          <t>63,4%</t>
+          <t>63,79%</t>
         </is>
       </c>
       <c r="W18" s="2" t="inlineStr">
         <is>
-          <t>75,33%</t>
+          <t>75,74%</t>
         </is>
       </c>
     </row>
@@ -11241,7 +11241,7 @@
       </c>
       <c r="F20" s="2" t="inlineStr">
         <is>
-          <t>4023</t>
+          <t>4123</t>
         </is>
       </c>
       <c r="G20" s="2" t="inlineStr">
@@ -11256,7 +11256,7 @@
       </c>
       <c r="I20" s="2" t="inlineStr">
         <is>
-          <t>9,74%</t>
+          <t>9,98%</t>
         </is>
       </c>
       <c r="J20" s="2" t="inlineStr">
@@ -11271,12 +11271,12 @@
       </c>
       <c r="L20" s="2" t="inlineStr">
         <is>
-          <t>643</t>
+          <t>646</t>
         </is>
       </c>
       <c r="M20" s="2" t="inlineStr">
         <is>
-          <t>4844</t>
+          <t>5370</t>
         </is>
       </c>
       <c r="N20" s="2" t="inlineStr">
@@ -11286,12 +11286,12 @@
       </c>
       <c r="O20" s="2" t="inlineStr">
         <is>
-          <t>1,48%</t>
+          <t>1,49%</t>
         </is>
       </c>
       <c r="P20" s="2" t="inlineStr">
         <is>
-          <t>11,15%</t>
+          <t>12,36%</t>
         </is>
       </c>
       <c r="Q20" s="2" t="inlineStr">
@@ -11306,12 +11306,12 @@
       </c>
       <c r="S20" s="2" t="inlineStr">
         <is>
-          <t>1236</t>
+          <t>1224</t>
         </is>
       </c>
       <c r="T20" s="2" t="inlineStr">
         <is>
-          <t>7092</t>
+          <t>7084</t>
         </is>
       </c>
       <c r="U20" s="2" t="inlineStr">
@@ -11321,12 +11321,12 @@
       </c>
       <c r="V20" s="2" t="inlineStr">
         <is>
-          <t>1,46%</t>
+          <t>1,44%</t>
         </is>
       </c>
       <c r="W20" s="2" t="inlineStr">
         <is>
-          <t>8,37%</t>
+          <t>8,36%</t>
         </is>
       </c>
     </row>
@@ -11349,12 +11349,12 @@
       </c>
       <c r="E21" s="2" t="inlineStr">
         <is>
-          <t>5749</t>
+          <t>5594</t>
         </is>
       </c>
       <c r="F21" s="2" t="inlineStr">
         <is>
-          <t>14416</t>
+          <t>14663</t>
         </is>
       </c>
       <c r="G21" s="2" t="inlineStr">
@@ -11364,12 +11364,12 @@
       </c>
       <c r="H21" s="2" t="inlineStr">
         <is>
-          <t>13,92%</t>
+          <t>13,54%</t>
         </is>
       </c>
       <c r="I21" s="2" t="inlineStr">
         <is>
-          <t>34,9%</t>
+          <t>35,5%</t>
         </is>
       </c>
       <c r="J21" s="2" t="inlineStr">
@@ -11384,12 +11384,12 @@
       </c>
       <c r="L21" s="2" t="inlineStr">
         <is>
-          <t>5374</t>
+          <t>5182</t>
         </is>
       </c>
       <c r="M21" s="2" t="inlineStr">
         <is>
-          <t>13507</t>
+          <t>14201</t>
         </is>
       </c>
       <c r="N21" s="2" t="inlineStr">
@@ -11399,12 +11399,12 @@
       </c>
       <c r="O21" s="2" t="inlineStr">
         <is>
-          <t>12,37%</t>
+          <t>11,93%</t>
         </is>
       </c>
       <c r="P21" s="2" t="inlineStr">
         <is>
-          <t>31,1%</t>
+          <t>32,7%</t>
         </is>
       </c>
       <c r="Q21" s="2" t="inlineStr">
@@ -11419,12 +11419,12 @@
       </c>
       <c r="S21" s="2" t="inlineStr">
         <is>
-          <t>13284</t>
+          <t>12902</t>
         </is>
       </c>
       <c r="T21" s="2" t="inlineStr">
         <is>
-          <t>25619</t>
+          <t>24847</t>
         </is>
       </c>
       <c r="U21" s="2" t="inlineStr">
@@ -11434,12 +11434,12 @@
       </c>
       <c r="V21" s="2" t="inlineStr">
         <is>
-          <t>15,68%</t>
+          <t>15,23%</t>
         </is>
       </c>
       <c r="W21" s="2" t="inlineStr">
         <is>
-          <t>30,23%</t>
+          <t>29,32%</t>
         </is>
       </c>
     </row>
@@ -11462,12 +11462,12 @@
       </c>
       <c r="E22" s="2" t="inlineStr">
         <is>
-          <t>25597</t>
+          <t>25572</t>
         </is>
       </c>
       <c r="F22" s="2" t="inlineStr">
         <is>
-          <t>34993</t>
+          <t>34739</t>
         </is>
       </c>
       <c r="G22" s="2" t="inlineStr">
@@ -11477,12 +11477,12 @@
       </c>
       <c r="H22" s="2" t="inlineStr">
         <is>
-          <t>61,97%</t>
+          <t>61,91%</t>
         </is>
       </c>
       <c r="I22" s="2" t="inlineStr">
         <is>
-          <t>84,71%</t>
+          <t>84,1%</t>
         </is>
       </c>
       <c r="J22" s="2" t="inlineStr">
@@ -11497,12 +11497,12 @@
       </c>
       <c r="L22" s="2" t="inlineStr">
         <is>
-          <t>27377</t>
+          <t>26762</t>
         </is>
       </c>
       <c r="M22" s="2" t="inlineStr">
         <is>
-          <t>36444</t>
+          <t>36755</t>
         </is>
       </c>
       <c r="N22" s="2" t="inlineStr">
@@ -11512,12 +11512,12 @@
       </c>
       <c r="O22" s="2" t="inlineStr">
         <is>
-          <t>63,04%</t>
+          <t>61,62%</t>
         </is>
       </c>
       <c r="P22" s="2" t="inlineStr">
         <is>
-          <t>83,91%</t>
+          <t>84,63%</t>
         </is>
       </c>
       <c r="Q22" s="2" t="inlineStr">
@@ -11532,12 +11532,12 @@
       </c>
       <c r="S22" s="2" t="inlineStr">
         <is>
-          <t>55922</t>
+          <t>56299</t>
         </is>
       </c>
       <c r="T22" s="2" t="inlineStr">
         <is>
-          <t>68735</t>
+          <t>69552</t>
         </is>
       </c>
       <c r="U22" s="2" t="inlineStr">
@@ -11547,12 +11547,12 @@
       </c>
       <c r="V22" s="2" t="inlineStr">
         <is>
-          <t>65,99%</t>
+          <t>66,44%</t>
         </is>
       </c>
       <c r="W22" s="2" t="inlineStr">
         <is>
-          <t>81,12%</t>
+          <t>82,08%</t>
         </is>
       </c>
     </row>
@@ -11692,12 +11692,12 @@
       </c>
       <c r="E24" s="2" t="inlineStr">
         <is>
-          <t>3146</t>
+          <t>3010</t>
         </is>
       </c>
       <c r="F24" s="2" t="inlineStr">
         <is>
-          <t>10618</t>
+          <t>11113</t>
         </is>
       </c>
       <c r="G24" s="2" t="inlineStr">
@@ -11707,12 +11707,12 @@
       </c>
       <c r="H24" s="2" t="inlineStr">
         <is>
-          <t>5,88%</t>
+          <t>5,62%</t>
         </is>
       </c>
       <c r="I24" s="2" t="inlineStr">
         <is>
-          <t>19,84%</t>
+          <t>20,76%</t>
         </is>
       </c>
       <c r="J24" s="2" t="inlineStr">
@@ -11727,12 +11727,12 @@
       </c>
       <c r="L24" s="2" t="inlineStr">
         <is>
-          <t>5151</t>
+          <t>5121</t>
         </is>
       </c>
       <c r="M24" s="2" t="inlineStr">
         <is>
-          <t>15334</t>
+          <t>15595</t>
         </is>
       </c>
       <c r="N24" s="2" t="inlineStr">
@@ -11742,12 +11742,12 @@
       </c>
       <c r="O24" s="2" t="inlineStr">
         <is>
-          <t>9,17%</t>
+          <t>9,12%</t>
         </is>
       </c>
       <c r="P24" s="2" t="inlineStr">
         <is>
-          <t>27,3%</t>
+          <t>27,76%</t>
         </is>
       </c>
       <c r="Q24" s="2" t="inlineStr">
@@ -11762,12 +11762,12 @@
       </c>
       <c r="S24" s="2" t="inlineStr">
         <is>
-          <t>10173</t>
+          <t>10408</t>
         </is>
       </c>
       <c r="T24" s="2" t="inlineStr">
         <is>
-          <t>22276</t>
+          <t>23312</t>
         </is>
       </c>
       <c r="U24" s="2" t="inlineStr">
@@ -11777,12 +11777,12 @@
       </c>
       <c r="V24" s="2" t="inlineStr">
         <is>
-          <t>9,27%</t>
+          <t>9,49%</t>
         </is>
       </c>
       <c r="W24" s="2" t="inlineStr">
         <is>
-          <t>20,31%</t>
+          <t>21,25%</t>
         </is>
       </c>
     </row>
@@ -11805,12 +11805,12 @@
       </c>
       <c r="E25" s="2" t="inlineStr">
         <is>
-          <t>7304</t>
+          <t>7885</t>
         </is>
       </c>
       <c r="F25" s="2" t="inlineStr">
         <is>
-          <t>17096</t>
+          <t>17438</t>
         </is>
       </c>
       <c r="G25" s="2" t="inlineStr">
@@ -11820,12 +11820,12 @@
       </c>
       <c r="H25" s="2" t="inlineStr">
         <is>
-          <t>13,65%</t>
+          <t>14,73%</t>
         </is>
       </c>
       <c r="I25" s="2" t="inlineStr">
         <is>
-          <t>31,94%</t>
+          <t>32,58%</t>
         </is>
       </c>
       <c r="J25" s="2" t="inlineStr">
@@ -11840,12 +11840,12 @@
       </c>
       <c r="L25" s="2" t="inlineStr">
         <is>
-          <t>7584</t>
+          <t>7501</t>
         </is>
       </c>
       <c r="M25" s="2" t="inlineStr">
         <is>
-          <t>17806</t>
+          <t>18346</t>
         </is>
       </c>
       <c r="N25" s="2" t="inlineStr">
@@ -11855,12 +11855,12 @@
       </c>
       <c r="O25" s="2" t="inlineStr">
         <is>
-          <t>13,5%</t>
+          <t>13,35%</t>
         </is>
       </c>
       <c r="P25" s="2" t="inlineStr">
         <is>
-          <t>31,7%</t>
+          <t>32,66%</t>
         </is>
       </c>
       <c r="Q25" s="2" t="inlineStr">
@@ -11875,12 +11875,12 @@
       </c>
       <c r="S25" s="2" t="inlineStr">
         <is>
-          <t>16671</t>
+          <t>17531</t>
         </is>
       </c>
       <c r="T25" s="2" t="inlineStr">
         <is>
-          <t>32132</t>
+          <t>32455</t>
         </is>
       </c>
       <c r="U25" s="2" t="inlineStr">
@@ -11890,12 +11890,12 @@
       </c>
       <c r="V25" s="2" t="inlineStr">
         <is>
-          <t>15,2%</t>
+          <t>15,98%</t>
         </is>
       </c>
       <c r="W25" s="2" t="inlineStr">
         <is>
-          <t>29,29%</t>
+          <t>29,58%</t>
         </is>
       </c>
     </row>
@@ -11918,12 +11918,12 @@
       </c>
       <c r="E26" s="2" t="inlineStr">
         <is>
-          <t>29556</t>
+          <t>29511</t>
         </is>
       </c>
       <c r="F26" s="2" t="inlineStr">
         <is>
-          <t>40511</t>
+          <t>40599</t>
         </is>
       </c>
       <c r="G26" s="2" t="inlineStr">
@@ -11933,82 +11933,82 @@
       </c>
       <c r="H26" s="2" t="inlineStr">
         <is>
+          <t>55,13%</t>
+        </is>
+      </c>
+      <c r="I26" s="2" t="inlineStr">
+        <is>
+          <t>75,85%</t>
+        </is>
+      </c>
+      <c r="J26" s="2" t="inlineStr">
+        <is>
+          <t>45</t>
+        </is>
+      </c>
+      <c r="K26" s="2" t="inlineStr">
+        <is>
+          <t>34586</t>
+        </is>
+      </c>
+      <c r="L26" s="2" t="inlineStr">
+        <is>
+          <t>28175</t>
+        </is>
+      </c>
+      <c r="M26" s="2" t="inlineStr">
+        <is>
+          <t>40808</t>
+        </is>
+      </c>
+      <c r="N26" s="2" t="inlineStr">
+        <is>
+          <t>61,57%</t>
+        </is>
+      </c>
+      <c r="O26" s="2" t="inlineStr">
+        <is>
+          <t>50,15%</t>
+        </is>
+      </c>
+      <c r="P26" s="2" t="inlineStr">
+        <is>
+          <t>72,64%</t>
+        </is>
+      </c>
+      <c r="Q26" s="2" t="inlineStr">
+        <is>
+          <t>97</t>
+        </is>
+      </c>
+      <c r="R26" s="2" t="inlineStr">
+        <is>
+          <t>69853</t>
+        </is>
+      </c>
+      <c r="S26" s="2" t="inlineStr">
+        <is>
+          <t>60574</t>
+        </is>
+      </c>
+      <c r="T26" s="2" t="inlineStr">
+        <is>
+          <t>78024</t>
+        </is>
+      </c>
+      <c r="U26" s="2" t="inlineStr">
+        <is>
+          <t>63,68%</t>
+        </is>
+      </c>
+      <c r="V26" s="2" t="inlineStr">
+        <is>
           <t>55,22%</t>
         </is>
       </c>
-      <c r="I26" s="2" t="inlineStr">
-        <is>
-          <t>75,68%</t>
-        </is>
-      </c>
-      <c r="J26" s="2" t="inlineStr">
-        <is>
-          <t>45</t>
-        </is>
-      </c>
-      <c r="K26" s="2" t="inlineStr">
-        <is>
-          <t>34586</t>
-        </is>
-      </c>
-      <c r="L26" s="2" t="inlineStr">
-        <is>
-          <t>28552</t>
-        </is>
-      </c>
-      <c r="M26" s="2" t="inlineStr">
-        <is>
-          <t>40534</t>
-        </is>
-      </c>
-      <c r="N26" s="2" t="inlineStr">
-        <is>
-          <t>61,57%</t>
-        </is>
-      </c>
-      <c r="O26" s="2" t="inlineStr">
-        <is>
-          <t>50,83%</t>
-        </is>
-      </c>
-      <c r="P26" s="2" t="inlineStr">
-        <is>
-          <t>72,16%</t>
-        </is>
-      </c>
-      <c r="Q26" s="2" t="inlineStr">
-        <is>
-          <t>97</t>
-        </is>
-      </c>
-      <c r="R26" s="2" t="inlineStr">
-        <is>
-          <t>69853</t>
-        </is>
-      </c>
-      <c r="S26" s="2" t="inlineStr">
-        <is>
-          <t>61658</t>
-        </is>
-      </c>
-      <c r="T26" s="2" t="inlineStr">
-        <is>
-          <t>77772</t>
-        </is>
-      </c>
-      <c r="U26" s="2" t="inlineStr">
-        <is>
-          <t>63,68%</t>
-        </is>
-      </c>
-      <c r="V26" s="2" t="inlineStr">
-        <is>
-          <t>56,2%</t>
-        </is>
-      </c>
       <c r="W26" s="2" t="inlineStr">
         <is>
-          <t>70,89%</t>
+          <t>71,12%</t>
         </is>
       </c>
     </row>
@@ -12148,12 +12148,12 @@
       </c>
       <c r="E28" s="2" t="inlineStr">
         <is>
-          <t>16589</t>
+          <t>16074</t>
         </is>
       </c>
       <c r="F28" s="2" t="inlineStr">
         <is>
-          <t>31067</t>
+          <t>29550</t>
         </is>
       </c>
       <c r="G28" s="2" t="inlineStr">
@@ -12163,12 +12163,12 @@
       </c>
       <c r="H28" s="2" t="inlineStr">
         <is>
-          <t>12,46%</t>
+          <t>12,07%</t>
         </is>
       </c>
       <c r="I28" s="2" t="inlineStr">
         <is>
-          <t>23,33%</t>
+          <t>22,19%</t>
         </is>
       </c>
       <c r="J28" s="2" t="inlineStr">
@@ -12183,12 +12183,12 @@
       </c>
       <c r="L28" s="2" t="inlineStr">
         <is>
-          <t>10448</t>
+          <t>10101</t>
         </is>
       </c>
       <c r="M28" s="2" t="inlineStr">
         <is>
-          <t>23068</t>
+          <t>22335</t>
         </is>
       </c>
       <c r="N28" s="2" t="inlineStr">
@@ -12198,12 +12198,12 @@
       </c>
       <c r="O28" s="2" t="inlineStr">
         <is>
-          <t>7,46%</t>
+          <t>7,22%</t>
         </is>
       </c>
       <c r="P28" s="2" t="inlineStr">
         <is>
-          <t>16,48%</t>
+          <t>15,96%</t>
         </is>
       </c>
       <c r="Q28" s="2" t="inlineStr">
@@ -12218,12 +12218,12 @@
       </c>
       <c r="S28" s="2" t="inlineStr">
         <is>
-          <t>29221</t>
+          <t>29636</t>
         </is>
       </c>
       <c r="T28" s="2" t="inlineStr">
         <is>
-          <t>48255</t>
+          <t>47792</t>
         </is>
       </c>
       <c r="U28" s="2" t="inlineStr">
@@ -12233,12 +12233,12 @@
       </c>
       <c r="V28" s="2" t="inlineStr">
         <is>
-          <t>10,7%</t>
+          <t>10,85%</t>
         </is>
       </c>
       <c r="W28" s="2" t="inlineStr">
         <is>
-          <t>17,67%</t>
+          <t>17,5%</t>
         </is>
       </c>
     </row>
@@ -12261,12 +12261,12 @@
       </c>
       <c r="E29" s="2" t="inlineStr">
         <is>
-          <t>30384</t>
+          <t>30517</t>
         </is>
       </c>
       <c r="F29" s="2" t="inlineStr">
         <is>
-          <t>47575</t>
+          <t>46985</t>
         </is>
       </c>
       <c r="G29" s="2" t="inlineStr">
@@ -12276,12 +12276,12 @@
       </c>
       <c r="H29" s="2" t="inlineStr">
         <is>
-          <t>22,81%</t>
+          <t>22,91%</t>
         </is>
       </c>
       <c r="I29" s="2" t="inlineStr">
         <is>
-          <t>35,72%</t>
+          <t>35,28%</t>
         </is>
       </c>
       <c r="J29" s="2" t="inlineStr">
@@ -12296,12 +12296,12 @@
       </c>
       <c r="L29" s="2" t="inlineStr">
         <is>
-          <t>31867</t>
+          <t>32378</t>
         </is>
       </c>
       <c r="M29" s="2" t="inlineStr">
         <is>
-          <t>49094</t>
+          <t>50305</t>
         </is>
       </c>
       <c r="N29" s="2" t="inlineStr">
@@ -12311,12 +12311,12 @@
       </c>
       <c r="O29" s="2" t="inlineStr">
         <is>
-          <t>22,77%</t>
+          <t>23,13%</t>
         </is>
       </c>
       <c r="P29" s="2" t="inlineStr">
         <is>
-          <t>35,07%</t>
+          <t>35,94%</t>
         </is>
       </c>
       <c r="Q29" s="2" t="inlineStr">
@@ -12331,12 +12331,12 @@
       </c>
       <c r="S29" s="2" t="inlineStr">
         <is>
-          <t>67250</t>
+          <t>66887</t>
         </is>
       </c>
       <c r="T29" s="2" t="inlineStr">
         <is>
-          <t>90945</t>
+          <t>91429</t>
         </is>
       </c>
       <c r="U29" s="2" t="inlineStr">
@@ -12346,12 +12346,12 @@
       </c>
       <c r="V29" s="2" t="inlineStr">
         <is>
-          <t>24,62%</t>
+          <t>24,49%</t>
         </is>
       </c>
       <c r="W29" s="2" t="inlineStr">
         <is>
-          <t>33,3%</t>
+          <t>33,47%</t>
         </is>
       </c>
     </row>
@@ -12374,12 +12374,12 @@
       </c>
       <c r="E30" s="2" t="inlineStr">
         <is>
-          <t>62399</t>
+          <t>62782</t>
         </is>
       </c>
       <c r="F30" s="2" t="inlineStr">
         <is>
-          <t>81534</t>
+          <t>80953</t>
         </is>
       </c>
       <c r="G30" s="2" t="inlineStr">
@@ -12389,12 +12389,12 @@
       </c>
       <c r="H30" s="2" t="inlineStr">
         <is>
-          <t>46,85%</t>
+          <t>47,14%</t>
         </is>
       </c>
       <c r="I30" s="2" t="inlineStr">
         <is>
-          <t>61,22%</t>
+          <t>60,79%</t>
         </is>
       </c>
       <c r="J30" s="2" t="inlineStr">
@@ -12409,12 +12409,12 @@
       </c>
       <c r="L30" s="2" t="inlineStr">
         <is>
-          <t>73928</t>
+          <t>74037</t>
         </is>
       </c>
       <c r="M30" s="2" t="inlineStr">
         <is>
-          <t>94159</t>
+          <t>93791</t>
         </is>
       </c>
       <c r="N30" s="2" t="inlineStr">
@@ -12424,12 +12424,12 @@
       </c>
       <c r="O30" s="2" t="inlineStr">
         <is>
-          <t>52,82%</t>
+          <t>52,9%</t>
         </is>
       </c>
       <c r="P30" s="2" t="inlineStr">
         <is>
-          <t>67,27%</t>
+          <t>67,01%</t>
         </is>
       </c>
       <c r="Q30" s="2" t="inlineStr">
@@ -12444,12 +12444,12 @@
       </c>
       <c r="S30" s="2" t="inlineStr">
         <is>
-          <t>143685</t>
+          <t>143118</t>
         </is>
       </c>
       <c r="T30" s="2" t="inlineStr">
         <is>
-          <t>169435</t>
+          <t>170340</t>
         </is>
       </c>
       <c r="U30" s="2" t="inlineStr">
@@ -12459,12 +12459,12 @@
       </c>
       <c r="V30" s="2" t="inlineStr">
         <is>
-          <t>52,6%</t>
+          <t>52,4%</t>
         </is>
       </c>
       <c r="W30" s="2" t="inlineStr">
         <is>
-          <t>62,03%</t>
+          <t>62,36%</t>
         </is>
       </c>
     </row>
@@ -12604,12 +12604,12 @@
       </c>
       <c r="E32" s="2" t="inlineStr">
         <is>
-          <t>20458</t>
+          <t>20203</t>
         </is>
       </c>
       <c r="F32" s="2" t="inlineStr">
         <is>
-          <t>35000</t>
+          <t>35320</t>
         </is>
       </c>
       <c r="G32" s="2" t="inlineStr">
@@ -12619,12 +12619,12 @@
       </c>
       <c r="H32" s="2" t="inlineStr">
         <is>
-          <t>12,85%</t>
+          <t>12,69%</t>
         </is>
       </c>
       <c r="I32" s="2" t="inlineStr">
         <is>
-          <t>21,99%</t>
+          <t>22,19%</t>
         </is>
       </c>
       <c r="J32" s="2" t="inlineStr">
@@ -12639,12 +12639,12 @@
       </c>
       <c r="L32" s="2" t="inlineStr">
         <is>
-          <t>22267</t>
+          <t>22241</t>
         </is>
       </c>
       <c r="M32" s="2" t="inlineStr">
         <is>
-          <t>38758</t>
+          <t>38914</t>
         </is>
       </c>
       <c r="N32" s="2" t="inlineStr">
@@ -12654,12 +12654,12 @@
       </c>
       <c r="O32" s="2" t="inlineStr">
         <is>
-          <t>13,52%</t>
+          <t>13,5%</t>
         </is>
       </c>
       <c r="P32" s="2" t="inlineStr">
         <is>
-          <t>23,53%</t>
+          <t>23,63%</t>
         </is>
       </c>
       <c r="Q32" s="2" t="inlineStr">
@@ -12674,12 +12674,12 @@
       </c>
       <c r="S32" s="2" t="inlineStr">
         <is>
-          <t>46632</t>
+          <t>46776</t>
         </is>
       </c>
       <c r="T32" s="2" t="inlineStr">
         <is>
-          <t>67766</t>
+          <t>68591</t>
         </is>
       </c>
       <c r="U32" s="2" t="inlineStr">
@@ -12689,12 +12689,12 @@
       </c>
       <c r="V32" s="2" t="inlineStr">
         <is>
-          <t>14,4%</t>
+          <t>14,44%</t>
         </is>
       </c>
       <c r="W32" s="2" t="inlineStr">
         <is>
-          <t>20,92%</t>
+          <t>21,18%</t>
         </is>
       </c>
     </row>
@@ -12717,12 +12717,12 @@
       </c>
       <c r="E33" s="2" t="inlineStr">
         <is>
-          <t>18038</t>
+          <t>18097</t>
         </is>
       </c>
       <c r="F33" s="2" t="inlineStr">
         <is>
-          <t>32300</t>
+          <t>32413</t>
         </is>
       </c>
       <c r="G33" s="2" t="inlineStr">
@@ -12732,12 +12732,12 @@
       </c>
       <c r="H33" s="2" t="inlineStr">
         <is>
-          <t>11,33%</t>
+          <t>11,37%</t>
         </is>
       </c>
       <c r="I33" s="2" t="inlineStr">
         <is>
-          <t>20,29%</t>
+          <t>20,36%</t>
         </is>
       </c>
       <c r="J33" s="2" t="inlineStr">
@@ -12752,12 +12752,12 @@
       </c>
       <c r="L33" s="2" t="inlineStr">
         <is>
-          <t>20760</t>
+          <t>20800</t>
         </is>
       </c>
       <c r="M33" s="2" t="inlineStr">
         <is>
-          <t>36038</t>
+          <t>35428</t>
         </is>
       </c>
       <c r="N33" s="2" t="inlineStr">
@@ -12767,12 +12767,12 @@
       </c>
       <c r="O33" s="2" t="inlineStr">
         <is>
-          <t>12,6%</t>
+          <t>12,63%</t>
         </is>
       </c>
       <c r="P33" s="2" t="inlineStr">
         <is>
-          <t>21,88%</t>
+          <t>21,51%</t>
         </is>
       </c>
       <c r="Q33" s="2" t="inlineStr">
@@ -12787,12 +12787,12 @@
       </c>
       <c r="S33" s="2" t="inlineStr">
         <is>
-          <t>41870</t>
+          <t>42728</t>
         </is>
       </c>
       <c r="T33" s="2" t="inlineStr">
         <is>
-          <t>63018</t>
+          <t>63372</t>
         </is>
       </c>
       <c r="U33" s="2" t="inlineStr">
@@ -12802,12 +12802,12 @@
       </c>
       <c r="V33" s="2" t="inlineStr">
         <is>
-          <t>12,93%</t>
+          <t>13,19%</t>
         </is>
       </c>
       <c r="W33" s="2" t="inlineStr">
         <is>
-          <t>19,46%</t>
+          <t>19,57%</t>
         </is>
       </c>
     </row>
@@ -12830,12 +12830,12 @@
       </c>
       <c r="E34" s="2" t="inlineStr">
         <is>
-          <t>98452</t>
+          <t>98419</t>
         </is>
       </c>
       <c r="F34" s="2" t="inlineStr">
         <is>
-          <t>116287</t>
+          <t>116682</t>
         </is>
       </c>
       <c r="G34" s="2" t="inlineStr">
@@ -12845,12 +12845,12 @@
       </c>
       <c r="H34" s="2" t="inlineStr">
         <is>
-          <t>61,86%</t>
+          <t>61,84%</t>
         </is>
       </c>
       <c r="I34" s="2" t="inlineStr">
         <is>
-          <t>73,06%</t>
+          <t>73,31%</t>
         </is>
       </c>
       <c r="J34" s="2" t="inlineStr">
@@ -12865,12 +12865,12 @@
       </c>
       <c r="L34" s="2" t="inlineStr">
         <is>
-          <t>96899</t>
+          <t>96964</t>
         </is>
       </c>
       <c r="M34" s="2" t="inlineStr">
         <is>
-          <t>116462</t>
+          <t>116816</t>
         </is>
       </c>
       <c r="N34" s="2" t="inlineStr">
@@ -12880,12 +12880,12 @@
       </c>
       <c r="O34" s="2" t="inlineStr">
         <is>
-          <t>58,83%</t>
+          <t>58,87%</t>
         </is>
       </c>
       <c r="P34" s="2" t="inlineStr">
         <is>
-          <t>70,71%</t>
+          <t>70,92%</t>
         </is>
       </c>
       <c r="Q34" s="2" t="inlineStr">
@@ -12900,12 +12900,12 @@
       </c>
       <c r="S34" s="2" t="inlineStr">
         <is>
-          <t>200368</t>
+          <t>202403</t>
         </is>
       </c>
       <c r="T34" s="2" t="inlineStr">
         <is>
-          <t>227417</t>
+          <t>227690</t>
         </is>
       </c>
       <c r="U34" s="2" t="inlineStr">
@@ -12915,12 +12915,12 @@
       </c>
       <c r="V34" s="2" t="inlineStr">
         <is>
-          <t>61,87%</t>
+          <t>62,49%</t>
         </is>
       </c>
       <c r="W34" s="2" t="inlineStr">
         <is>
-          <t>70,22%</t>
+          <t>70,3%</t>
         </is>
       </c>
     </row>
@@ -13060,12 +13060,12 @@
       </c>
       <c r="E36" s="2" t="inlineStr">
         <is>
-          <t>121796</t>
+          <t>121123</t>
         </is>
       </c>
       <c r="F36" s="2" t="inlineStr">
         <is>
-          <t>156203</t>
+          <t>155373</t>
         </is>
       </c>
       <c r="G36" s="2" t="inlineStr">
@@ -13075,12 +13075,12 @@
       </c>
       <c r="H36" s="2" t="inlineStr">
         <is>
-          <t>17,67%</t>
+          <t>17,58%</t>
         </is>
       </c>
       <c r="I36" s="2" t="inlineStr">
         <is>
-          <t>22,67%</t>
+          <t>22,55%</t>
         </is>
       </c>
       <c r="J36" s="2" t="inlineStr">
@@ -13095,12 +13095,12 @@
       </c>
       <c r="L36" s="2" t="inlineStr">
         <is>
-          <t>121927</t>
+          <t>121841</t>
         </is>
       </c>
       <c r="M36" s="2" t="inlineStr">
         <is>
-          <t>157045</t>
+          <t>155888</t>
         </is>
       </c>
       <c r="N36" s="2" t="inlineStr">
@@ -13110,12 +13110,12 @@
       </c>
       <c r="O36" s="2" t="inlineStr">
         <is>
-          <t>16,84%</t>
+          <t>16,83%</t>
         </is>
       </c>
       <c r="P36" s="2" t="inlineStr">
         <is>
-          <t>21,69%</t>
+          <t>21,53%</t>
         </is>
       </c>
       <c r="Q36" s="2" t="inlineStr">
@@ -13130,12 +13130,12 @@
       </c>
       <c r="S36" s="2" t="inlineStr">
         <is>
-          <t>253969</t>
+          <t>254897</t>
         </is>
       </c>
       <c r="T36" s="2" t="inlineStr">
         <is>
-          <t>299064</t>
+          <t>300948</t>
         </is>
       </c>
       <c r="U36" s="2" t="inlineStr">
@@ -13145,12 +13145,12 @@
       </c>
       <c r="V36" s="2" t="inlineStr">
         <is>
-          <t>17,97%</t>
+          <t>18,04%</t>
         </is>
       </c>
       <c r="W36" s="2" t="inlineStr">
         <is>
-          <t>21,16%</t>
+          <t>21,3%</t>
         </is>
       </c>
     </row>
@@ -13173,12 +13173,12 @@
       </c>
       <c r="E37" s="2" t="inlineStr">
         <is>
-          <t>92911</t>
+          <t>92687</t>
         </is>
       </c>
       <c r="F37" s="2" t="inlineStr">
         <is>
-          <t>123823</t>
+          <t>124248</t>
         </is>
       </c>
       <c r="G37" s="2" t="inlineStr">
@@ -13188,12 +13188,12 @@
       </c>
       <c r="H37" s="2" t="inlineStr">
         <is>
-          <t>13,48%</t>
+          <t>13,45%</t>
         </is>
       </c>
       <c r="I37" s="2" t="inlineStr">
         <is>
-          <t>17,97%</t>
+          <t>18,03%</t>
         </is>
       </c>
       <c r="J37" s="2" t="inlineStr">
@@ -13208,12 +13208,12 @@
       </c>
       <c r="L37" s="2" t="inlineStr">
         <is>
-          <t>101670</t>
+          <t>99988</t>
         </is>
       </c>
       <c r="M37" s="2" t="inlineStr">
         <is>
-          <t>132128</t>
+          <t>132961</t>
         </is>
       </c>
       <c r="N37" s="2" t="inlineStr">
@@ -13223,12 +13223,12 @@
       </c>
       <c r="O37" s="2" t="inlineStr">
         <is>
-          <t>14,04%</t>
+          <t>13,81%</t>
         </is>
       </c>
       <c r="P37" s="2" t="inlineStr">
         <is>
-          <t>18,25%</t>
+          <t>18,36%</t>
         </is>
       </c>
       <c r="Q37" s="2" t="inlineStr">
@@ -13243,12 +13243,12 @@
       </c>
       <c r="S37" s="2" t="inlineStr">
         <is>
-          <t>200036</t>
+          <t>202845</t>
         </is>
       </c>
       <c r="T37" s="2" t="inlineStr">
         <is>
-          <t>246839</t>
+          <t>244968</t>
         </is>
       </c>
       <c r="U37" s="2" t="inlineStr">
@@ -13258,12 +13258,12 @@
       </c>
       <c r="V37" s="2" t="inlineStr">
         <is>
-          <t>14,15%</t>
+          <t>14,35%</t>
         </is>
       </c>
       <c r="W37" s="2" t="inlineStr">
         <is>
-          <t>17,47%</t>
+          <t>17,33%</t>
         </is>
       </c>
     </row>
@@ -13286,12 +13286,12 @@
       </c>
       <c r="E38" s="2" t="inlineStr">
         <is>
-          <t>422892</t>
+          <t>423121</t>
         </is>
       </c>
       <c r="F38" s="2" t="inlineStr">
         <is>
-          <t>463413</t>
+          <t>463199</t>
         </is>
       </c>
       <c r="G38" s="2" t="inlineStr">
@@ -13301,12 +13301,12 @@
       </c>
       <c r="H38" s="2" t="inlineStr">
         <is>
-          <t>61,37%</t>
+          <t>61,4%</t>
         </is>
       </c>
       <c r="I38" s="2" t="inlineStr">
         <is>
-          <t>67,25%</t>
+          <t>67,21%</t>
         </is>
       </c>
       <c r="J38" s="2" t="inlineStr">
@@ -13321,12 +13321,12 @@
       </c>
       <c r="L38" s="2" t="inlineStr">
         <is>
-          <t>447788</t>
+          <t>451236</t>
         </is>
       </c>
       <c r="M38" s="2" t="inlineStr">
         <is>
-          <t>490310</t>
+          <t>490771</t>
         </is>
       </c>
       <c r="N38" s="2" t="inlineStr">
@@ -13336,12 +13336,12 @@
       </c>
       <c r="O38" s="2" t="inlineStr">
         <is>
-          <t>61,84%</t>
+          <t>62,32%</t>
         </is>
       </c>
       <c r="P38" s="2" t="inlineStr">
         <is>
-          <t>67,71%</t>
+          <t>67,78%</t>
         </is>
       </c>
       <c r="Q38" s="2" t="inlineStr">
@@ -13356,12 +13356,12 @@
       </c>
       <c r="S38" s="2" t="inlineStr">
         <is>
-          <t>883189</t>
+          <t>886026</t>
         </is>
       </c>
       <c r="T38" s="2" t="inlineStr">
         <is>
-          <t>940397</t>
+          <t>944300</t>
         </is>
       </c>
       <c r="U38" s="2" t="inlineStr">
@@ -13371,12 +13371,12 @@
       </c>
       <c r="V38" s="2" t="inlineStr">
         <is>
-          <t>62,49%</t>
+          <t>62,7%</t>
         </is>
       </c>
       <c r="W38" s="2" t="inlineStr">
         <is>
-          <t>66,54%</t>
+          <t>66,82%</t>
         </is>
       </c>
     </row>
